--- a/research/traditional_assets/database/data/south_korea/south_korea_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_green_renewable_energy.xlsx
@@ -1397,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1534,22 +1534,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07463909418788275</v>
+        <v>0.07448624645241304</v>
       </c>
       <c r="C2">
-        <v>240.324038498848</v>
+        <v>238.4780797411832</v>
       </c>
       <c r="D2">
-        <v>228.224038498848</v>
+        <v>229.0010797411832</v>
       </c>
       <c r="E2">
-        <v>-131.9</v>
+        <v>-129.277</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.623</v>
       </c>
       <c r="G2">
         <v>12.1</v>
@@ -1570,28 +1570,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1319369</v>
       </c>
       <c r="N2">
-        <v>22.75333333333334</v>
+        <v>22.62139643333334</v>
       </c>
       <c r="O2">
-        <v>5.688333333333334</v>
+        <v>5.655349108333334</v>
       </c>
       <c r="P2">
-        <v>17.065</v>
+        <v>16.96604732500001</v>
       </c>
       <c r="Q2">
-        <v>18.145</v>
+        <v>18.046047325</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07463909418788275</v>
+        <v>0.07485757217415459</v>
       </c>
       <c r="T2">
-        <v>0.5780409979533054</v>
+        <v>0.5824200964226487</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>172.4561766521219</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1616,22 +1616,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07448624645241304</v>
+        <v>0.07433339871694333</v>
       </c>
       <c r="C3">
-        <v>238.4780797411832</v>
+        <v>236.6374302916171</v>
       </c>
       <c r="D3">
-        <v>229.0010797411832</v>
+        <v>229.7834302916171</v>
       </c>
       <c r="E3">
-        <v>-129.277</v>
+        <v>-126.654</v>
       </c>
       <c r="F3">
-        <v>2.623</v>
+        <v>5.246</v>
       </c>
       <c r="G3">
         <v>12.1</v>
@@ -1652,28 +1652,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M3">
-        <v>0.1319369</v>
+        <v>0.2638738</v>
       </c>
       <c r="N3">
-        <v>22.62139643333334</v>
+        <v>22.48945953333334</v>
       </c>
       <c r="O3">
-        <v>5.655349108333334</v>
+        <v>5.622364883333335</v>
       </c>
       <c r="P3">
-        <v>16.96604732500001</v>
+        <v>16.86709465000001</v>
       </c>
       <c r="Q3">
-        <v>18.046047325</v>
+        <v>17.94709465</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07485757217415459</v>
+        <v>0.07508050889484014</v>
       </c>
       <c r="T3">
-        <v>0.5824200964226487</v>
+        <v>0.5868885642485091</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>172.4561766521219</v>
+        <v>86.22808832606094</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1698,22 +1698,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07433339871694333</v>
+        <v>0.07418055098147362</v>
       </c>
       <c r="C4">
-        <v>236.6374302916171</v>
+        <v>234.8021447522432</v>
       </c>
       <c r="D4">
-        <v>229.7834302916171</v>
+        <v>230.5711447522432</v>
       </c>
       <c r="E4">
-        <v>-126.654</v>
+        <v>-124.031</v>
       </c>
       <c r="F4">
-        <v>5.246</v>
+        <v>7.869</v>
       </c>
       <c r="G4">
         <v>12.1</v>
@@ -1734,28 +1734,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M4">
-        <v>0.2638738</v>
+        <v>0.3958107</v>
       </c>
       <c r="N4">
-        <v>22.48945953333334</v>
+        <v>22.35752263333334</v>
       </c>
       <c r="O4">
-        <v>5.622364883333335</v>
+        <v>5.589380658333335</v>
       </c>
       <c r="P4">
-        <v>16.86709465000001</v>
+        <v>16.76814197500001</v>
       </c>
       <c r="Q4">
-        <v>17.94709465</v>
+        <v>17.848141975</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07508050889484014</v>
+        <v>0.07530804224894189</v>
       </c>
       <c r="T4">
-        <v>0.5868885642485091</v>
+        <v>0.5914491654316038</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>86.22808832606094</v>
+        <v>57.48539221737396</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1780,22 +1780,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07418055098147362</v>
+        <v>0.07402770324600393</v>
       </c>
       <c r="C5">
-        <v>234.8021447522432</v>
+        <v>232.9722784764499</v>
       </c>
       <c r="D5">
-        <v>230.5711447522432</v>
+        <v>231.3642784764499</v>
       </c>
       <c r="E5">
-        <v>-124.031</v>
+        <v>-121.408</v>
       </c>
       <c r="F5">
-        <v>7.869</v>
+        <v>10.492</v>
       </c>
       <c r="G5">
         <v>12.1</v>
@@ -1816,28 +1816,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M5">
-        <v>0.3958107</v>
+        <v>0.5277476</v>
       </c>
       <c r="N5">
-        <v>22.35752263333334</v>
+        <v>22.22558573333334</v>
       </c>
       <c r="O5">
-        <v>5.589380658333335</v>
+        <v>5.556396433333334</v>
       </c>
       <c r="P5">
-        <v>16.76814197500001</v>
+        <v>16.6691893</v>
       </c>
       <c r="Q5">
-        <v>17.848141975</v>
+        <v>17.7491893</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07530804224894189</v>
+        <v>0.07554031588125409</v>
       </c>
       <c r="T5">
-        <v>0.5914491654316038</v>
+        <v>0.5961047791393462</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>57.48539221737396</v>
+        <v>43.11404416303046</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1862,22 +1862,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07402770324600393</v>
+        <v>0.07387485551053423</v>
       </c>
       <c r="C6">
-        <v>232.9722784764499</v>
+        <v>231.1478875818879</v>
       </c>
       <c r="D6">
-        <v>231.3642784764499</v>
+        <v>232.162887581888</v>
       </c>
       <c r="E6">
-        <v>-121.408</v>
+        <v>-118.785</v>
       </c>
       <c r="F6">
-        <v>10.492</v>
+        <v>13.115</v>
       </c>
       <c r="G6">
         <v>12.1</v>
@@ -1898,28 +1898,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M6">
-        <v>0.5277476</v>
+        <v>0.6596845000000001</v>
       </c>
       <c r="N6">
-        <v>22.22558573333334</v>
+        <v>22.09364883333334</v>
       </c>
       <c r="O6">
-        <v>5.556396433333334</v>
+        <v>5.523412208333334</v>
       </c>
       <c r="P6">
-        <v>16.6691893</v>
+        <v>16.570236625</v>
       </c>
       <c r="Q6">
-        <v>17.7491893</v>
+        <v>17.65023662500001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07554031588125409</v>
+        <v>0.07577747948477287</v>
       </c>
       <c r="T6">
-        <v>0.5961047791393462</v>
+        <v>0.6008584057672517</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.11404416303046</v>
+        <v>34.49123533042437</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1944,22 +1944,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07387485551053423</v>
+        <v>0.0737220077750645</v>
       </c>
       <c r="C7">
-        <v>231.1478875818879</v>
+        <v>229.3290289637056</v>
       </c>
       <c r="D7">
-        <v>232.162887581888</v>
+        <v>232.9670289637056</v>
       </c>
       <c r="E7">
-        <v>-118.785</v>
+        <v>-116.162</v>
       </c>
       <c r="F7">
-        <v>13.115</v>
+        <v>15.738</v>
       </c>
       <c r="G7">
         <v>12.1</v>
@@ -1980,28 +1980,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M7">
-        <v>0.6596845000000001</v>
+        <v>0.7916214</v>
       </c>
       <c r="N7">
-        <v>22.09364883333334</v>
+        <v>21.96171193333334</v>
       </c>
       <c r="O7">
-        <v>5.523412208333334</v>
+        <v>5.490427983333334</v>
       </c>
       <c r="P7">
-        <v>16.570236625</v>
+        <v>16.47128395</v>
       </c>
       <c r="Q7">
-        <v>17.65023662500001</v>
+        <v>17.55128395000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07577747948477287</v>
+        <v>0.07601968912240906</v>
       </c>
       <c r="T7">
-        <v>0.6008584057672517</v>
+        <v>0.6057131733872403</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.49123533042437</v>
+        <v>28.74269610868697</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2026,22 +2026,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0737220077750645</v>
+        <v>0.07356916003959481</v>
       </c>
       <c r="C8">
-        <v>229.3290289637056</v>
+        <v>227.5157603080603</v>
       </c>
       <c r="D8">
-        <v>232.9670289637056</v>
+        <v>233.7767603080603</v>
       </c>
       <c r="E8">
-        <v>-116.162</v>
+        <v>-113.539</v>
       </c>
       <c r="F8">
-        <v>15.738</v>
+        <v>18.361</v>
       </c>
       <c r="G8">
         <v>12.1</v>
@@ -2062,28 +2062,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M8">
-        <v>0.7916213999999999</v>
+        <v>0.9235582999999999</v>
       </c>
       <c r="N8">
-        <v>21.96171193333334</v>
+        <v>21.82977503333334</v>
       </c>
       <c r="O8">
-        <v>5.490427983333334</v>
+        <v>5.457443758333334</v>
       </c>
       <c r="P8">
-        <v>16.47128395</v>
+        <v>16.372331275</v>
       </c>
       <c r="Q8">
-        <v>17.55128395000001</v>
+        <v>17.45233127500001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07601968912240906</v>
+        <v>0.07626710756945679</v>
       </c>
       <c r="T8">
-        <v>0.6057131733872403</v>
+        <v>0.6106723446119597</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.74269610868698</v>
+        <v>24.63659666458884</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2108,22 +2108,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07356916003959481</v>
+        <v>0.0734163123041251</v>
       </c>
       <c r="C9">
-        <v>227.5157603080603</v>
+        <v>225.7081401059141</v>
       </c>
       <c r="D9">
-        <v>233.7767603080603</v>
+        <v>234.5921401059141</v>
       </c>
       <c r="E9">
-        <v>-113.539</v>
+        <v>-110.916</v>
       </c>
       <c r="F9">
-        <v>18.361</v>
+        <v>20.984</v>
       </c>
       <c r="G9">
         <v>12.1</v>
@@ -2144,28 +2144,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M9">
-        <v>0.9235583000000002</v>
+        <v>1.0554952</v>
       </c>
       <c r="N9">
-        <v>21.82977503333334</v>
+        <v>21.69783813333334</v>
       </c>
       <c r="O9">
-        <v>5.457443758333334</v>
+        <v>5.424459533333335</v>
       </c>
       <c r="P9">
-        <v>16.372331275</v>
+        <v>16.2733786</v>
       </c>
       <c r="Q9">
-        <v>17.45233127500001</v>
+        <v>17.35337860000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07626710756945679</v>
+        <v>0.07651990467839685</v>
       </c>
       <c r="T9">
-        <v>0.6106723446119597</v>
+        <v>0.6157393239067819</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.63659666458883</v>
+        <v>21.55702208151524</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2190,22 +2190,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0734163123041251</v>
+        <v>0.0732634645686554</v>
       </c>
       <c r="C10">
-        <v>225.7081401059141</v>
+        <v>223.9062276671172</v>
       </c>
       <c r="D10">
-        <v>234.5921401059141</v>
+        <v>235.4132276671172</v>
       </c>
       <c r="E10">
-        <v>-110.916</v>
+        <v>-108.293</v>
       </c>
       <c r="F10">
-        <v>20.984</v>
+        <v>23.607</v>
       </c>
       <c r="G10">
         <v>12.1</v>
@@ -2226,28 +2226,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M10">
-        <v>1.0554952</v>
+        <v>1.1874321</v>
       </c>
       <c r="N10">
-        <v>21.69783813333334</v>
+        <v>21.56590123333334</v>
       </c>
       <c r="O10">
-        <v>5.424459533333335</v>
+        <v>5.391475308333335</v>
       </c>
       <c r="P10">
-        <v>16.2733786</v>
+        <v>16.174425925</v>
       </c>
       <c r="Q10">
-        <v>17.35337860000001</v>
+        <v>17.25442592500001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07651990467839685</v>
+        <v>0.07677825776775318</v>
       </c>
       <c r="T10">
-        <v>0.6157393239067819</v>
+        <v>0.6209176653839077</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.55702208151524</v>
+        <v>19.16179740579132</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2272,22 +2272,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0732634645686554</v>
+        <v>0.07311061683318569</v>
       </c>
       <c r="C11">
-        <v>223.9062276671172</v>
+        <v>222.1100831347897</v>
       </c>
       <c r="D11">
-        <v>235.4132276671172</v>
+        <v>236.2400831347897</v>
       </c>
       <c r="E11">
-        <v>-108.293</v>
+        <v>-105.67</v>
       </c>
       <c r="F11">
-        <v>23.607</v>
+        <v>26.23</v>
       </c>
       <c r="G11">
         <v>12.1</v>
@@ -2308,28 +2308,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M11">
-        <v>1.1874321</v>
+        <v>1.319369</v>
       </c>
       <c r="N11">
-        <v>21.56590123333334</v>
+        <v>21.43396433333334</v>
       </c>
       <c r="O11">
-        <v>5.391475308333335</v>
+        <v>5.358491083333334</v>
       </c>
       <c r="P11">
-        <v>16.174425925</v>
+        <v>16.07547325</v>
       </c>
       <c r="Q11">
-        <v>17.25442592500001</v>
+        <v>17.15547325</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07677825776775318</v>
+        <v>0.07704235203687299</v>
       </c>
       <c r="T11">
-        <v>0.6209176653839077</v>
+        <v>0.6262110811160808</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.16179740579132</v>
+        <v>17.24561766521218</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07311061683318569</v>
+        <v>0.07295776909771597</v>
       </c>
       <c r="C12">
-        <v>222.1100831347897</v>
+        <v>220.3197675000065</v>
       </c>
       <c r="D12">
-        <v>236.2400831347897</v>
+        <v>237.0727675000066</v>
       </c>
       <c r="E12">
-        <v>-105.67</v>
+        <v>-103.047</v>
       </c>
       <c r="F12">
-        <v>26.23</v>
+        <v>28.853</v>
       </c>
       <c r="G12">
         <v>12.1</v>
@@ -2390,28 +2390,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M12">
-        <v>1.319369</v>
+        <v>1.4513059</v>
       </c>
       <c r="N12">
-        <v>21.43396433333334</v>
+        <v>21.30202743333334</v>
       </c>
       <c r="O12">
-        <v>5.358491083333334</v>
+        <v>5.325506858333334</v>
       </c>
       <c r="P12">
-        <v>16.07547325</v>
+        <v>15.976520575</v>
       </c>
       <c r="Q12">
-        <v>17.15547325</v>
+        <v>17.056520575</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07704235203687299</v>
+        <v>0.07731238100866963</v>
       </c>
       <c r="T12">
-        <v>0.6262110811160808</v>
+        <v>0.6316234500107748</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.24561766521218</v>
+        <v>15.67783424110199</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2436,22 +2436,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07295776909771597</v>
+        <v>0.07280492136224627</v>
       </c>
       <c r="C13">
-        <v>220.3197675000065</v>
+        <v>218.5353426167945</v>
       </c>
       <c r="D13">
-        <v>237.0727675000066</v>
+        <v>237.9113426167945</v>
       </c>
       <c r="E13">
-        <v>-103.047</v>
+        <v>-100.424</v>
       </c>
       <c r="F13">
-        <v>28.853</v>
+        <v>31.476</v>
       </c>
       <c r="G13">
         <v>12.1</v>
@@ -2472,28 +2472,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M13">
-        <v>1.4513059</v>
+        <v>1.5832428</v>
       </c>
       <c r="N13">
-        <v>21.30202743333334</v>
+        <v>21.17009053333334</v>
       </c>
       <c r="O13">
-        <v>5.325506858333334</v>
+        <v>5.292522633333334</v>
       </c>
       <c r="P13">
-        <v>15.976520575</v>
+        <v>15.8775679</v>
       </c>
       <c r="Q13">
-        <v>17.056520575</v>
+        <v>16.9575679</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07731238100866963</v>
+        <v>0.07758854700255258</v>
       </c>
       <c r="T13">
-        <v>0.6316234500107748</v>
+        <v>0.637158827289439</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.67783424110199</v>
+        <v>14.37134805434349</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2518,22 +2518,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07280492136224627</v>
+        <v>0.07265207362677657</v>
       </c>
       <c r="C14">
-        <v>218.5353426167945</v>
+        <v>216.7568712174485</v>
       </c>
       <c r="D14">
-        <v>237.9113426167945</v>
+        <v>238.7558712174485</v>
       </c>
       <c r="E14">
-        <v>-100.424</v>
+        <v>-97.801</v>
       </c>
       <c r="F14">
-        <v>31.476</v>
+        <v>34.099</v>
       </c>
       <c r="G14">
         <v>12.1</v>
@@ -2554,28 +2554,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M14">
-        <v>1.5832428</v>
+        <v>1.7151797</v>
       </c>
       <c r="N14">
-        <v>21.17009053333334</v>
+        <v>21.03815363333334</v>
       </c>
       <c r="O14">
-        <v>5.292522633333334</v>
+        <v>5.259538408333334</v>
       </c>
       <c r="P14">
-        <v>15.8775679</v>
+        <v>15.778615225</v>
       </c>
       <c r="Q14">
-        <v>16.9575679</v>
+        <v>16.858615225</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07758854700255258</v>
+        <v>0.07787106163997307</v>
       </c>
       <c r="T14">
-        <v>0.637158827289439</v>
+        <v>0.6428214546204862</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.37134805434349</v>
+        <v>13.26585974247091</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2600,22 +2600,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07265207362677657</v>
+        <v>0.07265672589130685</v>
       </c>
       <c r="C15">
-        <v>216.7568712174485</v>
+        <v>214.1080776302265</v>
       </c>
       <c r="D15">
-        <v>238.7558712174485</v>
+        <v>238.7300776302265</v>
       </c>
       <c r="E15">
-        <v>-97.801</v>
+        <v>-95.178</v>
       </c>
       <c r="F15">
-        <v>34.099</v>
+        <v>36.72200000000001</v>
       </c>
       <c r="G15">
         <v>12.1</v>
@@ -2636,45 +2636,45 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M15">
-        <v>1.7151797</v>
+        <v>1.9021996</v>
       </c>
       <c r="N15">
-        <v>21.03815363333334</v>
+        <v>20.85113373333334</v>
       </c>
       <c r="O15">
-        <v>5.259538408333334</v>
+        <v>5.212783433333334</v>
       </c>
       <c r="P15">
-        <v>15.778615225</v>
+        <v>15.6383503</v>
       </c>
       <c r="Q15">
-        <v>16.858615225</v>
+        <v>16.7183503</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07787106163997307</v>
+        <v>0.07816014638524053</v>
       </c>
       <c r="T15">
-        <v>0.6428214546204862</v>
+        <v>0.6486157709592323</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.26585974247091</v>
+        <v>11.96159085162952</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2682,22 +2682,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07265672589130685</v>
+        <v>0.07251512815583715</v>
       </c>
       <c r="C16">
-        <v>214.1080776302265</v>
+        <v>212.2726438918497</v>
       </c>
       <c r="D16">
-        <v>238.7300776302265</v>
+        <v>239.5176438918497</v>
       </c>
       <c r="E16">
-        <v>-95.178</v>
+        <v>-92.55500000000001</v>
       </c>
       <c r="F16">
-        <v>36.72200000000001</v>
+        <v>39.34500000000001</v>
       </c>
       <c r="G16">
         <v>12.1</v>
@@ -2718,28 +2718,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M16">
-        <v>1.9021996</v>
+        <v>2.038071</v>
       </c>
       <c r="N16">
-        <v>20.85113373333334</v>
+        <v>20.71526233333334</v>
       </c>
       <c r="O16">
-        <v>5.212783433333334</v>
+        <v>5.178815583333334</v>
       </c>
       <c r="P16">
-        <v>15.6383503</v>
+        <v>15.53644675</v>
       </c>
       <c r="Q16">
-        <v>16.7183503</v>
+        <v>16.61644675</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07816014638524053</v>
+        <v>0.0784560331245143</v>
       </c>
       <c r="T16">
-        <v>0.6486157709592323</v>
+        <v>0.6545464241530076</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.96159085162952</v>
+        <v>11.16415146152088</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2764,22 +2764,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07251512815583715</v>
+        <v>0.07237353042036744</v>
       </c>
       <c r="C17">
-        <v>212.2726438918497</v>
+        <v>210.4424236868838</v>
       </c>
       <c r="D17">
-        <v>239.5176438918497</v>
+        <v>240.3104236868838</v>
       </c>
       <c r="E17">
-        <v>-92.55500000000001</v>
+        <v>-89.932</v>
       </c>
       <c r="F17">
-        <v>39.345</v>
+        <v>41.968</v>
       </c>
       <c r="G17">
         <v>12.1</v>
@@ -2800,28 +2800,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M17">
-        <v>2.038071</v>
+        <v>2.1739424</v>
       </c>
       <c r="N17">
-        <v>20.71526233333334</v>
+        <v>20.57939093333334</v>
       </c>
       <c r="O17">
-        <v>5.178815583333335</v>
+        <v>5.144847733333334</v>
       </c>
       <c r="P17">
-        <v>15.53644675</v>
+        <v>15.4345432</v>
       </c>
       <c r="Q17">
-        <v>16.61644675</v>
+        <v>16.5145432</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0784560331245143</v>
+        <v>0.07875896478615171</v>
       </c>
       <c r="T17">
-        <v>0.6545464241530076</v>
+        <v>0.6606182833752062</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.16415146152089</v>
+        <v>10.46639199517583</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2846,22 +2846,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07237353042036744</v>
+        <v>0.07223193268489775</v>
       </c>
       <c r="C18">
-        <v>210.4424236868838</v>
+        <v>208.6174689560929</v>
       </c>
       <c r="D18">
-        <v>240.3104236868838</v>
+        <v>241.1084689560929</v>
       </c>
       <c r="E18">
-        <v>-89.932</v>
+        <v>-87.309</v>
       </c>
       <c r="F18">
-        <v>41.968</v>
+        <v>44.59100000000001</v>
       </c>
       <c r="G18">
         <v>12.1</v>
@@ -2882,28 +2882,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M18">
-        <v>2.1739424</v>
+        <v>2.309813800000001</v>
       </c>
       <c r="N18">
-        <v>20.57939093333334</v>
+        <v>20.44351953333334</v>
       </c>
       <c r="O18">
-        <v>5.144847733333334</v>
+        <v>5.110879883333334</v>
       </c>
       <c r="P18">
-        <v>15.4345432</v>
+        <v>15.33263965</v>
       </c>
       <c r="Q18">
-        <v>16.5145432</v>
+        <v>16.41263965</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07875896478615171</v>
+        <v>0.0790691960059009</v>
       </c>
       <c r="T18">
-        <v>0.6606182833752062</v>
+        <v>0.6668364524581808</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.46639199517583</v>
+        <v>9.850721877812546</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2928,22 +2928,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07223193268489775</v>
+        <v>0.07231983494942804</v>
       </c>
       <c r="C19">
-        <v>208.6174689560929</v>
+        <v>205.4984289191863</v>
       </c>
       <c r="D19">
-        <v>241.1084689560929</v>
+        <v>240.6124289191863</v>
       </c>
       <c r="E19">
-        <v>-87.309</v>
+        <v>-84.68600000000001</v>
       </c>
       <c r="F19">
-        <v>44.59100000000001</v>
+        <v>47.21400000000001</v>
       </c>
       <c r="G19">
         <v>12.1</v>
@@ -2964,45 +2964,45 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M19">
-        <v>2.309813800000001</v>
+        <v>2.525949</v>
       </c>
       <c r="N19">
-        <v>20.44351953333334</v>
+        <v>20.22738433333334</v>
       </c>
       <c r="O19">
-        <v>5.110879883333334</v>
+        <v>5.056846083333334</v>
       </c>
       <c r="P19">
-        <v>15.33263965</v>
+        <v>15.17053825</v>
       </c>
       <c r="Q19">
-        <v>16.41263965</v>
+        <v>16.25053825000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0790691960059009</v>
+        <v>0.07938699384076589</v>
       </c>
       <c r="T19">
-        <v>0.6668364524581808</v>
+        <v>0.6732062842017155</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>9.850721877812546</v>
+        <v>9.007835602909376</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3010,22 +3010,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07231983494942804</v>
+        <v>0.07219098721395834</v>
       </c>
       <c r="C20">
-        <v>205.4984289191863</v>
+        <v>203.6032266694875</v>
       </c>
       <c r="D20">
-        <v>240.6124289191863</v>
+        <v>241.3402266694875</v>
       </c>
       <c r="E20">
-        <v>-84.68600000000001</v>
+        <v>-82.063</v>
       </c>
       <c r="F20">
-        <v>47.214</v>
+        <v>49.837</v>
       </c>
       <c r="G20">
         <v>12.1</v>
@@ -3046,28 +3046,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M20">
-        <v>2.525949</v>
+        <v>2.6662795</v>
       </c>
       <c r="N20">
-        <v>20.22738433333334</v>
+        <v>20.08705383333334</v>
       </c>
       <c r="O20">
-        <v>5.056846083333334</v>
+        <v>5.021763458333334</v>
       </c>
       <c r="P20">
-        <v>15.17053825</v>
+        <v>15.065290375</v>
       </c>
       <c r="Q20">
-        <v>16.25053825000001</v>
+        <v>16.145290375</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07938699384076589</v>
+        <v>0.07971263853575103</v>
       </c>
       <c r="T20">
-        <v>0.6732062842017155</v>
+        <v>0.679733395741387</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.007835602909378</v>
+        <v>8.533738992229935</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3092,22 +3092,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07219098721395834</v>
+        <v>0.07206213947848862</v>
       </c>
       <c r="C21">
-        <v>203.6032266694875</v>
+        <v>201.712440622384</v>
       </c>
       <c r="D21">
-        <v>241.3402266694875</v>
+        <v>242.072440622384</v>
       </c>
       <c r="E21">
-        <v>-82.063</v>
+        <v>-79.44</v>
       </c>
       <c r="F21">
-        <v>49.837</v>
+        <v>52.46000000000001</v>
       </c>
       <c r="G21">
         <v>12.1</v>
@@ -3128,28 +3128,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M21">
-        <v>2.6662795</v>
+        <v>2.80661</v>
       </c>
       <c r="N21">
-        <v>20.08705383333334</v>
+        <v>19.94672333333334</v>
       </c>
       <c r="O21">
-        <v>5.021763458333334</v>
+        <v>4.986680833333335</v>
       </c>
       <c r="P21">
-        <v>15.065290375</v>
+        <v>14.9600425</v>
       </c>
       <c r="Q21">
-        <v>16.145290375</v>
+        <v>16.04004250000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07971263853575103</v>
+        <v>0.08004642434811077</v>
       </c>
       <c r="T21">
-        <v>0.679733395741387</v>
+        <v>0.6864236850695502</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.533738992229935</v>
+        <v>8.107052042618438</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3174,22 +3174,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07206213947848862</v>
+        <v>0.07193329174301891</v>
       </c>
       <c r="C22">
-        <v>201.712440622384</v>
+        <v>199.8261110957991</v>
       </c>
       <c r="D22">
-        <v>242.072440622384</v>
+        <v>242.8091110957991</v>
       </c>
       <c r="E22">
-        <v>-79.44</v>
+        <v>-76.81700000000001</v>
       </c>
       <c r="F22">
-        <v>52.46000000000001</v>
+        <v>55.08300000000001</v>
       </c>
       <c r="G22">
         <v>12.1</v>
@@ -3210,28 +3210,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M22">
-        <v>2.80661</v>
+        <v>2.9469405</v>
       </c>
       <c r="N22">
-        <v>19.94672333333334</v>
+        <v>19.80639283333334</v>
       </c>
       <c r="O22">
-        <v>4.986680833333335</v>
+        <v>4.951598208333334</v>
       </c>
       <c r="P22">
-        <v>14.9600425</v>
+        <v>14.854794625</v>
       </c>
       <c r="Q22">
-        <v>16.04004250000001</v>
+        <v>15.934794625</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08004642434811077</v>
+        <v>0.08038866043420115</v>
       </c>
       <c r="T22">
-        <v>0.6864236850695502</v>
+        <v>0.6932833488110847</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.107052042618438</v>
+        <v>7.721001945350894</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3256,22 +3256,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07193329174301891</v>
+        <v>0.0719364440075492</v>
       </c>
       <c r="C23">
-        <v>199.8261110957991</v>
+        <v>197.185034925434</v>
       </c>
       <c r="D23">
-        <v>242.8091110957991</v>
+        <v>242.791034925434</v>
       </c>
       <c r="E23">
-        <v>-76.81700000000001</v>
+        <v>-74.194</v>
       </c>
       <c r="F23">
-        <v>55.083</v>
+        <v>57.706</v>
       </c>
       <c r="G23">
         <v>12.1</v>
@@ -3292,45 +3292,45 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M23">
-        <v>2.9469405</v>
+        <v>3.1334358</v>
       </c>
       <c r="N23">
-        <v>19.80639283333334</v>
+        <v>19.61989753333334</v>
       </c>
       <c r="O23">
-        <v>4.951598208333334</v>
+        <v>4.904974383333334</v>
       </c>
       <c r="P23">
-        <v>14.854794625</v>
+        <v>14.71492315</v>
       </c>
       <c r="Q23">
-        <v>15.934794625</v>
+        <v>15.79492315</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08038866043420115</v>
+        <v>0.08073967180455026</v>
       </c>
       <c r="T23">
-        <v>0.6932833488110847</v>
+        <v>0.7003189013665047</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.721001945350895</v>
+        <v>7.261464662315192</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3338,22 +3338,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0719364440075492</v>
+        <v>0.07181359627207949</v>
       </c>
       <c r="C24">
-        <v>197.185034925434</v>
+        <v>195.2684832892851</v>
       </c>
       <c r="D24">
-        <v>242.791034925434</v>
+        <v>243.4974832892851</v>
       </c>
       <c r="E24">
-        <v>-74.194</v>
+        <v>-71.571</v>
       </c>
       <c r="F24">
-        <v>57.706</v>
+        <v>60.32900000000001</v>
       </c>
       <c r="G24">
         <v>12.1</v>
@@ -3374,28 +3374,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M24">
-        <v>3.1334358</v>
+        <v>3.275864700000001</v>
       </c>
       <c r="N24">
-        <v>19.61989753333334</v>
+        <v>19.47746863333334</v>
       </c>
       <c r="O24">
-        <v>4.904974383333334</v>
+        <v>4.869367158333334</v>
       </c>
       <c r="P24">
-        <v>14.71492315</v>
+        <v>14.608101475</v>
       </c>
       <c r="Q24">
-        <v>15.79492315</v>
+        <v>15.688101475</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08073967180455026</v>
+        <v>0.08109980035334999</v>
       </c>
       <c r="T24">
-        <v>0.7003189013665047</v>
+        <v>0.7075371955467408</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.261464662315192</v>
+        <v>6.945748807431923</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3420,22 +3420,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07181359627207949</v>
+        <v>0.0716907485366098</v>
       </c>
       <c r="C25">
-        <v>195.2684832892851</v>
+        <v>193.3560547515776</v>
       </c>
       <c r="D25">
-        <v>243.4974832892851</v>
+        <v>244.2080547515776</v>
       </c>
       <c r="E25">
-        <v>-71.571</v>
+        <v>-68.94800000000001</v>
       </c>
       <c r="F25">
-        <v>60.32900000000001</v>
+        <v>62.95200000000001</v>
       </c>
       <c r="G25">
         <v>12.1</v>
@@ -3456,28 +3456,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M25">
-        <v>3.275864700000001</v>
+        <v>3.4182936</v>
       </c>
       <c r="N25">
-        <v>19.47746863333334</v>
+        <v>19.33503973333334</v>
       </c>
       <c r="O25">
-        <v>4.869367158333334</v>
+        <v>4.833759933333335</v>
       </c>
       <c r="P25">
-        <v>14.608101475</v>
+        <v>14.5012798</v>
       </c>
       <c r="Q25">
-        <v>15.688101475</v>
+        <v>15.5812798</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08109980035334999</v>
+        <v>0.08146940596922342</v>
       </c>
       <c r="T25">
-        <v>0.7075371955467408</v>
+        <v>0.7149454448369831</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.945748807431923</v>
+        <v>6.65634260712226</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3502,22 +3502,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0716907485366098</v>
+        <v>0.07156790080114009</v>
       </c>
       <c r="C26">
-        <v>193.3560547515776</v>
+        <v>191.4477855138854</v>
       </c>
       <c r="D26">
-        <v>244.2080547515776</v>
+        <v>244.9227855138854</v>
       </c>
       <c r="E26">
-        <v>-68.94800000000001</v>
+        <v>-66.325</v>
       </c>
       <c r="F26">
-        <v>62.952</v>
+        <v>65.575</v>
       </c>
       <c r="G26">
         <v>12.1</v>
@@ -3538,28 +3538,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M26">
-        <v>3.4182936</v>
+        <v>3.5607225</v>
       </c>
       <c r="N26">
-        <v>19.33503973333334</v>
+        <v>19.19261083333334</v>
       </c>
       <c r="O26">
-        <v>4.833759933333335</v>
+        <v>4.798152708333334</v>
       </c>
       <c r="P26">
-        <v>14.5012798</v>
+        <v>14.394458125</v>
       </c>
       <c r="Q26">
-        <v>15.5812798</v>
+        <v>15.474458125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08146940596922342</v>
+        <v>0.08184886773485345</v>
       </c>
       <c r="T26">
-        <v>0.7149454448369831</v>
+        <v>0.7225512474416318</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.65634260712226</v>
+        <v>6.39008890283737</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3584,22 +3584,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07156790080114009</v>
+        <v>0.07144505306567038</v>
       </c>
       <c r="C27">
-        <v>191.4477855138854</v>
+        <v>189.5437122028347</v>
       </c>
       <c r="D27">
-        <v>244.9227855138854</v>
+        <v>245.6417122028347</v>
       </c>
       <c r="E27">
-        <v>-66.325</v>
+        <v>-63.702</v>
       </c>
       <c r="F27">
-        <v>65.575</v>
+        <v>68.19800000000001</v>
       </c>
       <c r="G27">
         <v>12.1</v>
@@ -3620,28 +3620,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M27">
-        <v>3.5607225</v>
+        <v>3.7031514</v>
       </c>
       <c r="N27">
-        <v>19.19261083333334</v>
+        <v>19.05018193333334</v>
       </c>
       <c r="O27">
-        <v>4.798152708333334</v>
+        <v>4.762545483333334</v>
       </c>
       <c r="P27">
-        <v>14.394458125</v>
+        <v>14.28763645</v>
       </c>
       <c r="Q27">
-        <v>15.474458125</v>
+        <v>15.36763645</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08184886773485345</v>
+        <v>0.08223858522387889</v>
       </c>
       <c r="T27">
-        <v>0.7225512474416318</v>
+        <v>0.7303626122788387</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.39008890283737</v>
+        <v>6.14431625272824</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3666,22 +3666,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07144505306567038</v>
+        <v>0.07152470533020067</v>
       </c>
       <c r="C28">
-        <v>189.5437122028347</v>
+        <v>186.454092860833</v>
       </c>
       <c r="D28">
-        <v>245.6417122028347</v>
+        <v>245.175092860833</v>
       </c>
       <c r="E28">
-        <v>-63.702</v>
+        <v>-61.07899999999999</v>
       </c>
       <c r="F28">
-        <v>68.19800000000001</v>
+        <v>70.82100000000001</v>
       </c>
       <c r="G28">
         <v>12.1</v>
@@ -3702,45 +3702,45 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M28">
-        <v>3.7031514</v>
+        <v>3.916401300000001</v>
       </c>
       <c r="N28">
-        <v>19.05018193333334</v>
+        <v>18.83693203333334</v>
       </c>
       <c r="O28">
-        <v>4.762545483333334</v>
+        <v>4.709233008333334</v>
       </c>
       <c r="P28">
-        <v>14.28763645</v>
+        <v>14.127699025</v>
       </c>
       <c r="Q28">
-        <v>15.36763645</v>
+        <v>15.207699025</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08223858522387889</v>
+        <v>0.08263897990438449</v>
       </c>
       <c r="T28">
-        <v>0.7303626122788387</v>
+        <v>0.7383879871115855</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.14431625272824</v>
+        <v>5.809755331593148</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3748,22 +3748,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07152470533020067</v>
+        <v>0.07140935759473097</v>
       </c>
       <c r="C29">
-        <v>186.454092860833</v>
+        <v>184.5074004375976</v>
       </c>
       <c r="D29">
-        <v>245.175092860833</v>
+        <v>245.8514004375976</v>
       </c>
       <c r="E29">
-        <v>-61.07899999999999</v>
+        <v>-58.45599999999999</v>
       </c>
       <c r="F29">
-        <v>70.82100000000001</v>
+        <v>73.44400000000002</v>
       </c>
       <c r="G29">
         <v>12.1</v>
@@ -3784,28 +3784,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M29">
-        <v>3.916401300000001</v>
+        <v>4.061453200000001</v>
       </c>
       <c r="N29">
-        <v>18.83693203333334</v>
+        <v>18.69188013333333</v>
       </c>
       <c r="O29">
-        <v>4.709233008333334</v>
+        <v>4.672970033333334</v>
       </c>
       <c r="P29">
-        <v>14.127699025</v>
+        <v>14.0189101</v>
       </c>
       <c r="Q29">
-        <v>15.207699025</v>
+        <v>15.0989101</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08263897990438449</v>
+        <v>0.08305049665934856</v>
       </c>
       <c r="T29">
-        <v>0.7383879871115855</v>
+        <v>0.7466362890230196</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.809755331593148</v>
+        <v>5.602264069750534</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3830,22 +3830,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07140935759473097</v>
+        <v>0.07129400985926125</v>
       </c>
       <c r="C30">
-        <v>184.5074004375976</v>
+        <v>182.5644494802992</v>
       </c>
       <c r="D30">
-        <v>245.8514004375976</v>
+        <v>246.5314494802992</v>
       </c>
       <c r="E30">
-        <v>-58.45599999999999</v>
+        <v>-55.833</v>
       </c>
       <c r="F30">
-        <v>73.44400000000002</v>
+        <v>76.06700000000001</v>
       </c>
       <c r="G30">
         <v>12.1</v>
@@ -3866,28 +3866,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M30">
-        <v>4.061453200000001</v>
+        <v>4.2065051</v>
       </c>
       <c r="N30">
-        <v>18.69188013333333</v>
+        <v>18.54682823333334</v>
       </c>
       <c r="O30">
-        <v>4.672970033333334</v>
+        <v>4.636707058333334</v>
       </c>
       <c r="P30">
-        <v>14.0189101</v>
+        <v>13.910121175</v>
       </c>
       <c r="Q30">
-        <v>15.0989101</v>
+        <v>14.990121175</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08305049665934856</v>
+        <v>0.08347360543557923</v>
       </c>
       <c r="T30">
-        <v>0.7466362890230196</v>
+        <v>0.7551169374671701</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.602264069750534</v>
+        <v>5.409082550103966</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3912,22 +3912,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07129400985926125</v>
+        <v>0.07117866212379155</v>
       </c>
       <c r="C31">
-        <v>182.5644494802992</v>
+        <v>180.6252711228405</v>
       </c>
       <c r="D31">
-        <v>246.5314494802992</v>
+        <v>247.2152711228405</v>
       </c>
       <c r="E31">
-        <v>-55.83300000000001</v>
+        <v>-53.21000000000001</v>
       </c>
       <c r="F31">
-        <v>76.06699999999999</v>
+        <v>78.69</v>
       </c>
       <c r="G31">
         <v>12.1</v>
@@ -3948,28 +3948,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M31">
-        <v>4.206505099999999</v>
+        <v>4.351557</v>
       </c>
       <c r="N31">
-        <v>18.54682823333334</v>
+        <v>18.40177633333334</v>
       </c>
       <c r="O31">
-        <v>4.636707058333334</v>
+        <v>4.600444083333334</v>
       </c>
       <c r="P31">
-        <v>13.910121175</v>
+        <v>13.80133225</v>
       </c>
       <c r="Q31">
-        <v>14.990121175</v>
+        <v>14.88133225</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08347360543557923</v>
+        <v>0.08390880303398793</v>
       </c>
       <c r="T31">
-        <v>0.7551169374671701</v>
+        <v>0.7638398901525821</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.409082550103967</v>
+        <v>5.228779798433834</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3994,22 +3994,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07117866212379155</v>
+        <v>0.07106331438832184</v>
       </c>
       <c r="C32">
-        <v>180.6252711228405</v>
+        <v>178.6898968455181</v>
       </c>
       <c r="D32">
-        <v>247.2152711228405</v>
+        <v>247.9028968455181</v>
       </c>
       <c r="E32">
-        <v>-53.21000000000001</v>
+        <v>-50.587</v>
       </c>
       <c r="F32">
-        <v>78.69</v>
+        <v>81.313</v>
       </c>
       <c r="G32">
         <v>12.1</v>
@@ -4030,28 +4030,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M32">
-        <v>4.351557</v>
+        <v>4.4966089</v>
       </c>
       <c r="N32">
-        <v>18.40177633333334</v>
+        <v>18.25672443333334</v>
       </c>
       <c r="O32">
-        <v>4.600444083333334</v>
+        <v>4.564181108333335</v>
       </c>
       <c r="P32">
-        <v>13.80133225</v>
+        <v>13.692543325</v>
       </c>
       <c r="Q32">
-        <v>14.88133225</v>
+        <v>14.772543325</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08390880303398793</v>
+        <v>0.0843566150555389</v>
       </c>
       <c r="T32">
-        <v>0.7638398901525821</v>
+        <v>0.772815682046267</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.228779798433834</v>
+        <v>5.060109482355323</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4076,22 +4076,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07106331438832184</v>
+        <v>0.07094796665285213</v>
       </c>
       <c r="C33">
-        <v>178.6898968455181</v>
+        <v>176.7583584798535</v>
       </c>
       <c r="D33">
-        <v>247.9028968455181</v>
+        <v>248.5943584798535</v>
       </c>
       <c r="E33">
-        <v>-50.587</v>
+        <v>-47.964</v>
       </c>
       <c r="F33">
-        <v>81.313</v>
+        <v>83.93600000000001</v>
       </c>
       <c r="G33">
         <v>12.1</v>
@@ -4112,28 +4112,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M33">
-        <v>4.4966089</v>
+        <v>4.6416608</v>
       </c>
       <c r="N33">
-        <v>18.25672443333334</v>
+        <v>18.11167253333334</v>
       </c>
       <c r="O33">
-        <v>4.564181108333335</v>
+        <v>4.527918133333334</v>
       </c>
       <c r="P33">
-        <v>13.692543325</v>
+        <v>13.5837544</v>
       </c>
       <c r="Q33">
-        <v>14.772543325</v>
+        <v>14.6637544</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0843566150555389</v>
+        <v>0.08481759801890021</v>
       </c>
       <c r="T33">
-        <v>0.772815682046267</v>
+        <v>0.782055467819178</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.060109482355323</v>
+        <v>4.901981061031718</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4158,22 +4158,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07094796665285213</v>
+        <v>0.07083261891738242</v>
       </c>
       <c r="C34">
-        <v>176.7583584798535</v>
+        <v>174.8306882135052</v>
       </c>
       <c r="D34">
-        <v>248.5943584798535</v>
+        <v>249.2896882135052</v>
       </c>
       <c r="E34">
-        <v>-47.964</v>
+        <v>-45.34099999999999</v>
       </c>
       <c r="F34">
-        <v>83.93600000000001</v>
+        <v>86.55900000000001</v>
       </c>
       <c r="G34">
         <v>12.1</v>
@@ -4194,28 +4194,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M34">
-        <v>4.6416608</v>
+        <v>4.786712700000001</v>
       </c>
       <c r="N34">
-        <v>18.11167253333334</v>
+        <v>17.96662063333333</v>
       </c>
       <c r="O34">
-        <v>4.527918133333334</v>
+        <v>4.491655158333334</v>
       </c>
       <c r="P34">
-        <v>13.5837544</v>
+        <v>13.474965475</v>
       </c>
       <c r="Q34">
-        <v>14.6637544</v>
+        <v>14.554965475</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08481759801890021</v>
+        <v>0.08529234166773497</v>
       </c>
       <c r="T34">
-        <v>0.782055467819178</v>
+        <v>0.7915710680927728</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.901981061031718</v>
+        <v>4.753436180394393</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4240,22 +4240,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07083261891738242</v>
+        <v>0.07071727118191272</v>
       </c>
       <c r="C35">
-        <v>174.8306882135052</v>
+        <v>172.9069185952631</v>
       </c>
       <c r="D35">
-        <v>249.2896882135052</v>
+        <v>249.9889185952631</v>
       </c>
       <c r="E35">
-        <v>-45.34099999999999</v>
+        <v>-42.71799999999999</v>
       </c>
       <c r="F35">
-        <v>86.55900000000001</v>
+        <v>89.18200000000002</v>
       </c>
       <c r="G35">
         <v>12.1</v>
@@ -4276,28 +4276,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M35">
-        <v>4.786712700000001</v>
+        <v>4.931764600000001</v>
       </c>
       <c r="N35">
-        <v>17.96662063333333</v>
+        <v>17.82156873333334</v>
       </c>
       <c r="O35">
-        <v>4.491655158333334</v>
+        <v>4.455392183333334</v>
       </c>
       <c r="P35">
-        <v>13.474965475</v>
+        <v>13.36617655</v>
       </c>
       <c r="Q35">
-        <v>14.554965475</v>
+        <v>14.44617655</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08529234166773497</v>
+        <v>0.08578147148774655</v>
       </c>
       <c r="T35">
-        <v>0.7915710680927728</v>
+        <v>0.8013750198898099</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.753436180394393</v>
+        <v>4.613629233912205</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4322,22 +4322,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07071727118191272</v>
+        <v>0.071258173446443</v>
       </c>
       <c r="C36">
-        <v>172.9069185952631</v>
+        <v>167.0384948125622</v>
       </c>
       <c r="D36">
-        <v>249.9889185952631</v>
+        <v>246.7434948125622</v>
       </c>
       <c r="E36">
-        <v>-42.71799999999999</v>
+        <v>-40.095</v>
       </c>
       <c r="F36">
-        <v>89.18200000000002</v>
+        <v>91.80500000000001</v>
       </c>
       <c r="G36">
         <v>12.1</v>
@@ -4358,45 +4358,45 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M36">
-        <v>4.931764600000001</v>
+        <v>5.306329000000001</v>
       </c>
       <c r="N36">
-        <v>17.82156873333334</v>
+        <v>17.44700433333334</v>
       </c>
       <c r="O36">
-        <v>4.455392183333334</v>
+        <v>4.361751083333334</v>
       </c>
       <c r="P36">
-        <v>13.36617655</v>
+        <v>13.08525325</v>
       </c>
       <c r="Q36">
-        <v>14.44617655</v>
+        <v>14.16525325</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08578147148774655</v>
+        <v>0.08628565145606618</v>
       </c>
       <c r="T36">
-        <v>0.8013750198898099</v>
+        <v>0.8114806317421404</v>
       </c>
       <c r="U36">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.613629233912205</v>
+        <v>4.28796128798899</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4404,22 +4404,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.071258173446443</v>
+        <v>0.0711615757109733</v>
       </c>
       <c r="C37">
-        <v>167.0384948125622</v>
+        <v>164.9888880617358</v>
       </c>
       <c r="D37">
-        <v>246.7434948125622</v>
+        <v>247.3168880617358</v>
       </c>
       <c r="E37">
-        <v>-40.095</v>
+        <v>-37.47199999999999</v>
       </c>
       <c r="F37">
-        <v>91.80500000000001</v>
+        <v>94.42800000000001</v>
       </c>
       <c r="G37">
         <v>12.1</v>
@@ -4440,28 +4440,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M37">
-        <v>5.306329000000001</v>
+        <v>5.457938400000001</v>
       </c>
       <c r="N37">
-        <v>17.44700433333334</v>
+        <v>17.29539493333334</v>
       </c>
       <c r="O37">
-        <v>4.361751083333334</v>
+        <v>4.323848733333334</v>
       </c>
       <c r="P37">
-        <v>13.08525325</v>
+        <v>12.9715462</v>
       </c>
       <c r="Q37">
-        <v>14.16525325</v>
+        <v>14.0515462</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08628565145606618</v>
+        <v>0.08680558704839579</v>
       </c>
       <c r="T37">
-        <v>0.8114806317421404</v>
+        <v>0.8219020439648561</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.28796128798899</v>
+        <v>4.168851252211519</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4486,22 +4486,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0711615757109733</v>
+        <v>0.0710649779755036</v>
       </c>
       <c r="C38">
-        <v>164.9888880617358</v>
+        <v>162.9419524705353</v>
       </c>
       <c r="D38">
-        <v>247.3168880617358</v>
+        <v>247.8929524705352</v>
       </c>
       <c r="E38">
-        <v>-37.47200000000001</v>
+        <v>-34.849</v>
       </c>
       <c r="F38">
-        <v>94.428</v>
+        <v>97.051</v>
       </c>
       <c r="G38">
         <v>12.1</v>
@@ -4522,28 +4522,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M38">
-        <v>5.457938400000001</v>
+        <v>5.609547800000001</v>
       </c>
       <c r="N38">
-        <v>17.29539493333334</v>
+        <v>17.14378553333334</v>
       </c>
       <c r="O38">
-        <v>4.323848733333334</v>
+        <v>4.285946383333334</v>
       </c>
       <c r="P38">
-        <v>12.9715462</v>
+        <v>12.85783915</v>
       </c>
       <c r="Q38">
-        <v>14.0515462</v>
+        <v>13.93783915</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08680558704839579</v>
+        <v>0.0873420285325454</v>
       </c>
       <c r="T38">
-        <v>0.8219020439648561</v>
+        <v>0.8326542946708329</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.168851252211519</v>
+        <v>4.056179596746343</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4568,22 +4568,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0710649779755036</v>
+        <v>0.07196588024003389</v>
       </c>
       <c r="C39">
-        <v>162.9419524705353</v>
+        <v>155.0483672530875</v>
       </c>
       <c r="D39">
-        <v>247.8929524705352</v>
+        <v>242.6223672530875</v>
       </c>
       <c r="E39">
-        <v>-34.849</v>
+        <v>-32.226</v>
       </c>
       <c r="F39">
-        <v>97.051</v>
+        <v>99.67400000000001</v>
       </c>
       <c r="G39">
         <v>12.1</v>
@@ -4604,45 +4604,45 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M39">
-        <v>5.609547800000001</v>
+        <v>6.1100162</v>
       </c>
       <c r="N39">
-        <v>17.14378553333334</v>
+        <v>16.64331713333334</v>
       </c>
       <c r="O39">
-        <v>4.285946383333334</v>
+        <v>4.160829283333334</v>
       </c>
       <c r="P39">
-        <v>12.85783915</v>
+        <v>12.48248785</v>
       </c>
       <c r="Q39">
-        <v>13.93783915</v>
+        <v>13.56248785</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0873420285325454</v>
+        <v>0.08789577458069983</v>
       </c>
       <c r="T39">
-        <v>0.8326542946708329</v>
+        <v>0.8437533921737765</v>
       </c>
       <c r="U39">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.056179596746343</v>
+        <v>3.72393993543476</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4650,22 +4650,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07196588024003389</v>
+        <v>0.07189553250456419</v>
       </c>
       <c r="C40">
-        <v>155.0483672530875</v>
+        <v>152.8288449792085</v>
       </c>
       <c r="D40">
-        <v>242.6223672530875</v>
+        <v>243.0258449792085</v>
       </c>
       <c r="E40">
-        <v>-32.226</v>
+        <v>-29.60299999999999</v>
       </c>
       <c r="F40">
-        <v>99.67400000000001</v>
+        <v>102.297</v>
       </c>
       <c r="G40">
         <v>12.1</v>
@@ -4686,28 +4686,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M40">
-        <v>6.1100162</v>
+        <v>6.270806100000001</v>
       </c>
       <c r="N40">
-        <v>16.64331713333334</v>
+        <v>16.48252723333334</v>
       </c>
       <c r="O40">
-        <v>4.160829283333334</v>
+        <v>4.120631808333334</v>
       </c>
       <c r="P40">
-        <v>12.48248785</v>
+        <v>12.361895425</v>
       </c>
       <c r="Q40">
-        <v>13.56248785</v>
+        <v>13.441895425</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08789577458069983</v>
+        <v>0.08846767623699048</v>
       </c>
       <c r="T40">
-        <v>0.8437533921737765</v>
+        <v>0.8552163945128822</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.72393993543476</v>
+        <v>3.628454296064637</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4732,22 +4732,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07189553250456419</v>
+        <v>0.07182518476909448</v>
       </c>
       <c r="C41">
-        <v>152.8288449792085</v>
+        <v>150.6106668967408</v>
       </c>
       <c r="D41">
-        <v>243.0258449792085</v>
+        <v>243.4306668967409</v>
       </c>
       <c r="E41">
-        <v>-29.60299999999999</v>
+        <v>-26.97999999999999</v>
       </c>
       <c r="F41">
-        <v>102.297</v>
+        <v>104.92</v>
       </c>
       <c r="G41">
         <v>12.1</v>
@@ -4768,28 +4768,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M41">
-        <v>6.270806100000001</v>
+        <v>6.431596000000001</v>
       </c>
       <c r="N41">
-        <v>16.48252723333334</v>
+        <v>16.32173733333334</v>
       </c>
       <c r="O41">
-        <v>4.120631808333334</v>
+        <v>4.080434333333335</v>
       </c>
       <c r="P41">
-        <v>12.361895425</v>
+        <v>12.241303</v>
       </c>
       <c r="Q41">
-        <v>13.441895425</v>
+        <v>13.321303</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08846767623699048</v>
+        <v>0.08905864128182414</v>
       </c>
       <c r="T41">
-        <v>0.8552163945128822</v>
+        <v>0.8670614969299582</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.628454296064637</v>
+        <v>3.537742938663022</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4814,22 +4814,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07182518476909448</v>
+        <v>0.07261583703362477</v>
       </c>
       <c r="C42">
-        <v>150.6106668967408</v>
+        <v>143.5139689927363</v>
       </c>
       <c r="D42">
-        <v>243.4306668967409</v>
+        <v>238.9569689927363</v>
       </c>
       <c r="E42">
-        <v>-26.97999999999999</v>
+        <v>-24.357</v>
       </c>
       <c r="F42">
-        <v>104.92</v>
+        <v>107.543</v>
       </c>
       <c r="G42">
         <v>12.1</v>
@@ -4850,45 +4850,45 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M42">
-        <v>6.431596000000001</v>
+        <v>6.893506300000001</v>
       </c>
       <c r="N42">
-        <v>16.32173733333334</v>
+        <v>15.85982703333334</v>
       </c>
       <c r="O42">
-        <v>4.080434333333335</v>
+        <v>3.964956758333334</v>
       </c>
       <c r="P42">
-        <v>12.241303</v>
+        <v>11.894870275</v>
       </c>
       <c r="Q42">
-        <v>13.321303</v>
+        <v>12.974870275</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08905864128182414</v>
+        <v>0.08966963904004199</v>
       </c>
       <c r="T42">
-        <v>0.8670614969299582</v>
+        <v>0.8793081282425282</v>
       </c>
       <c r="U42">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.537742938663022</v>
+        <v>3.300690873863905</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4896,22 +4896,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07261583703362477</v>
+        <v>0.07256648929815507</v>
       </c>
       <c r="C43">
-        <v>143.5139689927363</v>
+        <v>141.1653734792116</v>
       </c>
       <c r="D43">
-        <v>238.9569689927363</v>
+        <v>239.2313734792116</v>
       </c>
       <c r="E43">
-        <v>-24.357</v>
+        <v>-21.73399999999999</v>
       </c>
       <c r="F43">
-        <v>107.543</v>
+        <v>110.166</v>
       </c>
       <c r="G43">
         <v>12.1</v>
@@ -4932,28 +4932,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M43">
-        <v>6.893506300000001</v>
+        <v>7.061640600000001</v>
       </c>
       <c r="N43">
-        <v>15.85982703333334</v>
+        <v>15.69169273333334</v>
       </c>
       <c r="O43">
-        <v>3.964956758333334</v>
+        <v>3.922923183333334</v>
       </c>
       <c r="P43">
-        <v>11.894870275</v>
+        <v>11.76876955</v>
       </c>
       <c r="Q43">
-        <v>12.974870275</v>
+        <v>12.84876955</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08966963904004199</v>
+        <v>0.09030170568647425</v>
       </c>
       <c r="T43">
-        <v>0.8793081282425282</v>
+        <v>0.8919770571865662</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.300690873863905</v>
+        <v>3.222102995914764</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4978,22 +4978,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07256648929815507</v>
+        <v>0.07251714156268538</v>
       </c>
       <c r="C44">
-        <v>141.1653734792116</v>
+        <v>138.8174089109958</v>
       </c>
       <c r="D44">
-        <v>239.2313734792116</v>
+        <v>239.5064089109958</v>
       </c>
       <c r="E44">
-        <v>-21.73400000000001</v>
+        <v>-19.111</v>
       </c>
       <c r="F44">
-        <v>110.166</v>
+        <v>112.789</v>
       </c>
       <c r="G44">
         <v>12.1</v>
@@ -5014,28 +5014,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M44">
-        <v>7.0616406</v>
+        <v>7.229774900000001</v>
       </c>
       <c r="N44">
-        <v>15.69169273333334</v>
+        <v>15.52355843333334</v>
       </c>
       <c r="O44">
-        <v>3.922923183333334</v>
+        <v>3.880889608333334</v>
       </c>
       <c r="P44">
-        <v>11.76876955</v>
+        <v>11.642668825</v>
       </c>
       <c r="Q44">
-        <v>12.84876955</v>
+        <v>12.722668825</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09030170568647425</v>
+        <v>0.09095595010997432</v>
       </c>
       <c r="T44">
-        <v>0.8919770571865662</v>
+        <v>0.9050905099532018</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.222102995914764</v>
+        <v>3.147170368102793</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5060,22 +5060,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07251714156268538</v>
+        <v>0.07246779382721566</v>
       </c>
       <c r="C45">
-        <v>138.8174089109958</v>
+        <v>136.4700774667169</v>
       </c>
       <c r="D45">
-        <v>239.5064089109958</v>
+        <v>239.7820774667169</v>
       </c>
       <c r="E45">
-        <v>-19.111</v>
+        <v>-16.488</v>
       </c>
       <c r="F45">
-        <v>112.789</v>
+        <v>115.412</v>
       </c>
       <c r="G45">
         <v>12.1</v>
@@ -5096,28 +5096,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M45">
-        <v>7.229774900000001</v>
+        <v>7.397909200000001</v>
       </c>
       <c r="N45">
-        <v>15.52355843333334</v>
+        <v>15.35542413333334</v>
       </c>
       <c r="O45">
-        <v>3.880889608333334</v>
+        <v>3.838856033333334</v>
       </c>
       <c r="P45">
-        <v>11.642668825</v>
+        <v>11.5165681</v>
       </c>
       <c r="Q45">
-        <v>12.722668825</v>
+        <v>12.5965681</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09095595010997432</v>
+        <v>0.09163356040574225</v>
       </c>
       <c r="T45">
-        <v>0.9050905099532018</v>
+        <v>0.9186723003186462</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.147170368102793</v>
+        <v>3.07564376882773</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5142,22 +5142,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07246779382721566</v>
+        <v>0.07241844609174596</v>
       </c>
       <c r="C46">
-        <v>136.4700774667169</v>
+        <v>134.1233813350445</v>
       </c>
       <c r="D46">
-        <v>239.7820774667169</v>
+        <v>240.0583813350445</v>
       </c>
       <c r="E46">
-        <v>-16.488</v>
+        <v>-13.86499999999999</v>
       </c>
       <c r="F46">
-        <v>115.412</v>
+        <v>118.035</v>
       </c>
       <c r="G46">
         <v>12.1</v>
@@ -5178,28 +5178,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M46">
-        <v>7.397909200000001</v>
+        <v>7.566043500000001</v>
       </c>
       <c r="N46">
-        <v>15.35542413333334</v>
+        <v>15.18728983333334</v>
       </c>
       <c r="O46">
-        <v>3.838856033333334</v>
+        <v>3.796822458333334</v>
       </c>
       <c r="P46">
-        <v>11.5165681</v>
+        <v>11.390467375</v>
       </c>
       <c r="Q46">
-        <v>12.5965681</v>
+        <v>12.470467375</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09163356040574225</v>
+        <v>0.09233581107590172</v>
       </c>
       <c r="T46">
-        <v>0.9186723003186462</v>
+        <v>0.9327479739701064</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.07564376882773</v>
+        <v>3.007296129520447</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5224,22 +5224,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07241844609174596</v>
+        <v>0.07506009835627625</v>
       </c>
       <c r="C47">
-        <v>134.1233813350445</v>
+        <v>117.5527676054166</v>
       </c>
       <c r="D47">
-        <v>240.0583813350445</v>
+        <v>226.1107676054166</v>
       </c>
       <c r="E47">
-        <v>-13.86499999999999</v>
+        <v>-11.24199999999999</v>
       </c>
       <c r="F47">
-        <v>118.035</v>
+        <v>120.658</v>
       </c>
       <c r="G47">
         <v>12.1</v>
@@ -5260,45 +5260,45 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M47">
-        <v>7.566043500000001</v>
+        <v>8.675310200000002</v>
       </c>
       <c r="N47">
-        <v>15.18728983333334</v>
+        <v>14.07802313333334</v>
       </c>
       <c r="O47">
-        <v>3.796822458333334</v>
+        <v>3.519505783333334</v>
       </c>
       <c r="P47">
-        <v>11.390467375</v>
+        <v>10.55851735</v>
       </c>
       <c r="Q47">
-        <v>12.470467375</v>
+        <v>11.63851735</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09233581107590172</v>
+        <v>0.09306407103014118</v>
       </c>
       <c r="T47">
-        <v>0.9327479739701064</v>
+        <v>0.9473449688679172</v>
       </c>
       <c r="U47">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.007296129520447</v>
+        <v>2.622768847312611</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5306,22 +5306,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07506009835627625</v>
+        <v>0.07506925062080654</v>
       </c>
       <c r="C48">
-        <v>117.5527676054166</v>
+        <v>114.8842614878066</v>
       </c>
       <c r="D48">
-        <v>226.1107676054166</v>
+        <v>226.0652614878066</v>
       </c>
       <c r="E48">
-        <v>-11.24199999999999</v>
+        <v>-8.619</v>
       </c>
       <c r="F48">
-        <v>120.658</v>
+        <v>123.281</v>
       </c>
       <c r="G48">
         <v>12.1</v>
@@ -5342,28 +5342,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M48">
-        <v>8.675310200000002</v>
+        <v>8.8639039</v>
       </c>
       <c r="N48">
-        <v>14.07802313333334</v>
+        <v>13.88942943333334</v>
       </c>
       <c r="O48">
-        <v>3.519505783333334</v>
+        <v>3.472357358333334</v>
       </c>
       <c r="P48">
-        <v>10.55851735</v>
+        <v>10.417072075</v>
       </c>
       <c r="Q48">
-        <v>11.63851735</v>
+        <v>11.497072075</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09306407103014118</v>
+        <v>0.09381981249208779</v>
       </c>
       <c r="T48">
-        <v>0.9473449688679172</v>
+        <v>0.9624927937618717</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.622768847312611</v>
+        <v>2.566965254816598</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5388,22 +5388,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07506925062080654</v>
+        <v>0.07507840288533682</v>
       </c>
       <c r="C49">
-        <v>114.8842614878066</v>
+        <v>112.215773683257</v>
       </c>
       <c r="D49">
-        <v>226.0652614878066</v>
+        <v>226.019773683257</v>
       </c>
       <c r="E49">
-        <v>-8.619</v>
+        <v>-5.995999999999995</v>
       </c>
       <c r="F49">
-        <v>123.281</v>
+        <v>125.904</v>
       </c>
       <c r="G49">
         <v>12.1</v>
@@ -5424,28 +5424,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M49">
-        <v>8.8639039</v>
+        <v>9.052497600000001</v>
       </c>
       <c r="N49">
-        <v>13.88942943333334</v>
+        <v>13.70083573333334</v>
       </c>
       <c r="O49">
-        <v>3.472357358333334</v>
+        <v>3.425208933333334</v>
       </c>
       <c r="P49">
-        <v>10.417072075</v>
+        <v>10.2756268</v>
       </c>
       <c r="Q49">
-        <v>11.497072075</v>
+        <v>11.3556268</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09381981249208779</v>
+        <v>0.09460462093334004</v>
       </c>
       <c r="T49">
-        <v>0.9624927937618717</v>
+        <v>0.9782232273055939</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.566965254816598</v>
+        <v>2.513486812007919</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5470,22 +5470,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07507840288533682</v>
+        <v>0.07652080514986712</v>
       </c>
       <c r="C50">
-        <v>112.215773683257</v>
+        <v>102.6456173281341</v>
       </c>
       <c r="D50">
-        <v>226.019773683257</v>
+        <v>219.0726173281341</v>
       </c>
       <c r="E50">
-        <v>-5.996000000000009</v>
+        <v>-3.37299999999999</v>
       </c>
       <c r="F50">
-        <v>125.904</v>
+        <v>128.527</v>
       </c>
       <c r="G50">
         <v>12.1</v>
@@ -5506,45 +5506,45 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M50">
-        <v>9.052497600000001</v>
+        <v>9.742346600000001</v>
       </c>
       <c r="N50">
-        <v>13.70083573333334</v>
+        <v>13.01098673333334</v>
       </c>
       <c r="O50">
-        <v>3.425208933333334</v>
+        <v>3.252746683333334</v>
       </c>
       <c r="P50">
-        <v>10.2756268</v>
+        <v>9.758240050000001</v>
       </c>
       <c r="Q50">
-        <v>11.3556268</v>
+        <v>10.83824005</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09460462093334004</v>
+        <v>0.09542020617621003</v>
       </c>
       <c r="T50">
-        <v>0.9782232273055939</v>
+        <v>0.9945705405961284</v>
       </c>
       <c r="U50">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.513486812007919</v>
+        <v>2.335508504012096</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5552,22 +5552,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07652080514986712</v>
+        <v>0.07655920741439741</v>
       </c>
       <c r="C51">
-        <v>102.6456173281341</v>
+        <v>99.84348914501203</v>
       </c>
       <c r="D51">
-        <v>219.0726173281341</v>
+        <v>218.893489145012</v>
       </c>
       <c r="E51">
-        <v>-3.37299999999999</v>
+        <v>-0.75</v>
       </c>
       <c r="F51">
-        <v>128.527</v>
+        <v>131.15</v>
       </c>
       <c r="G51">
         <v>12.1</v>
@@ -5588,28 +5588,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M51">
-        <v>9.742346600000001</v>
+        <v>9.941170000000001</v>
       </c>
       <c r="N51">
-        <v>13.01098673333334</v>
+        <v>12.81216333333334</v>
       </c>
       <c r="O51">
-        <v>3.252746683333334</v>
+        <v>3.203040833333334</v>
       </c>
       <c r="P51">
-        <v>9.758240050000001</v>
+        <v>9.609122500000002</v>
       </c>
       <c r="Q51">
-        <v>10.83824005</v>
+        <v>10.6891225</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09542020617621003</v>
+        <v>0.09626841482879482</v>
       </c>
       <c r="T51">
-        <v>0.9945705405961284</v>
+        <v>1.011571746418285</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.335508504012096</v>
+        <v>2.288798333931855</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5634,22 +5634,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07655920741439741</v>
+        <v>0.0765976096789277</v>
       </c>
       <c r="C52">
-        <v>99.84348914501203</v>
+        <v>97.04165365653569</v>
       </c>
       <c r="D52">
-        <v>218.893489145012</v>
+        <v>218.7146536565357</v>
       </c>
       <c r="E52">
-        <v>-0.75</v>
+        <v>1.87299999999999</v>
       </c>
       <c r="F52">
-        <v>131.15</v>
+        <v>133.773</v>
       </c>
       <c r="G52">
         <v>12.1</v>
@@ -5670,28 +5670,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M52">
-        <v>9.941170000000001</v>
+        <v>10.1399934</v>
       </c>
       <c r="N52">
-        <v>12.81216333333334</v>
+        <v>12.61333993333334</v>
       </c>
       <c r="O52">
-        <v>3.203040833333334</v>
+        <v>3.153334983333334</v>
       </c>
       <c r="P52">
-        <v>9.609122500000002</v>
+        <v>9.460004950000004</v>
       </c>
       <c r="Q52">
-        <v>10.6891225</v>
+        <v>10.54000495</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09626841482879482</v>
+        <v>0.0971512442427096</v>
       </c>
       <c r="T52">
-        <v>1.011571746418285</v>
+        <v>1.029266879008692</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.288798333931855</v>
+        <v>2.243919935227309</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5716,22 +5716,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0765976096789277</v>
+        <v>0.076636011943458</v>
       </c>
       <c r="C53">
-        <v>97.04165365653569</v>
+        <v>94.24011014589806</v>
       </c>
       <c r="D53">
-        <v>218.7146536565357</v>
+        <v>218.5361101458981</v>
       </c>
       <c r="E53">
-        <v>1.87299999999999</v>
+        <v>4.496000000000009</v>
       </c>
       <c r="F53">
-        <v>133.773</v>
+        <v>136.396</v>
       </c>
       <c r="G53">
         <v>12.1</v>
@@ -5752,28 +5752,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M53">
-        <v>10.1399934</v>
+        <v>10.3388168</v>
       </c>
       <c r="N53">
-        <v>12.61333993333334</v>
+        <v>12.41451653333334</v>
       </c>
       <c r="O53">
-        <v>3.153334983333334</v>
+        <v>3.103629133333334</v>
       </c>
       <c r="P53">
-        <v>9.460004950000004</v>
+        <v>9.310887400000002</v>
       </c>
       <c r="Q53">
-        <v>10.54000495</v>
+        <v>10.3908874</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.0971512442427096</v>
+        <v>0.09807085821553749</v>
       </c>
       <c r="T53">
-        <v>1.029266879008692</v>
+        <v>1.047699308790366</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.243919935227309</v>
+        <v>2.200767628780629</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5798,22 +5798,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.076636011943458</v>
+        <v>0.07667441420798829</v>
       </c>
       <c r="C54">
-        <v>94.24011014589806</v>
+        <v>91.43885789863094</v>
       </c>
       <c r="D54">
-        <v>218.5361101458981</v>
+        <v>218.357857898631</v>
       </c>
       <c r="E54">
-        <v>4.496000000000009</v>
+        <v>7.119</v>
       </c>
       <c r="F54">
-        <v>136.396</v>
+        <v>139.019</v>
       </c>
       <c r="G54">
         <v>12.1</v>
@@ -5834,28 +5834,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M54">
-        <v>10.3388168</v>
+        <v>10.5376402</v>
       </c>
       <c r="N54">
-        <v>12.41451653333334</v>
+        <v>12.21569313333334</v>
       </c>
       <c r="O54">
-        <v>3.103629133333334</v>
+        <v>3.053923283333334</v>
       </c>
       <c r="P54">
-        <v>9.310887400000002</v>
+        <v>9.161769850000002</v>
       </c>
       <c r="Q54">
-        <v>10.3908874</v>
+        <v>10.24176985</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09807085821553749</v>
+        <v>0.09902960469784743</v>
       </c>
       <c r="T54">
-        <v>1.047699308790366</v>
+        <v>1.066916097286154</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.200767628780629</v>
+        <v>2.159243711256466</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5880,22 +5880,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07667441420798829</v>
+        <v>0.07671281647251858</v>
       </c>
       <c r="C55">
-        <v>91.43885789863094</v>
+        <v>88.63789620259516</v>
       </c>
       <c r="D55">
-        <v>218.357857898631</v>
+        <v>218.1798962025952</v>
       </c>
       <c r="E55">
-        <v>7.119</v>
+        <v>9.742000000000019</v>
       </c>
       <c r="F55">
-        <v>139.019</v>
+        <v>141.642</v>
       </c>
       <c r="G55">
         <v>12.1</v>
@@ -5916,28 +5916,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M55">
-        <v>10.5376402</v>
+        <v>10.7364636</v>
       </c>
       <c r="N55">
-        <v>12.21569313333334</v>
+        <v>12.01686973333334</v>
       </c>
       <c r="O55">
-        <v>3.053923283333334</v>
+        <v>3.004217433333334</v>
       </c>
       <c r="P55">
-        <v>9.161769850000002</v>
+        <v>9.012652300000001</v>
       </c>
       <c r="Q55">
-        <v>10.24176985</v>
+        <v>10.0926523</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09902960469784743</v>
+        <v>0.100030035809823</v>
       </c>
       <c r="T55">
-        <v>1.066916097286154</v>
+        <v>1.086968398325237</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.159243711256466</v>
+        <v>2.119257716603569</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5962,22 +5962,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07671281647251858</v>
+        <v>0.07675121873704888</v>
       </c>
       <c r="C56">
-        <v>88.63789620259516</v>
+        <v>85.83722434797133</v>
       </c>
       <c r="D56">
-        <v>218.1798962025952</v>
+        <v>218.0022243479713</v>
       </c>
       <c r="E56">
-        <v>9.742000000000019</v>
+        <v>12.36500000000001</v>
       </c>
       <c r="F56">
-        <v>141.642</v>
+        <v>144.265</v>
       </c>
       <c r="G56">
         <v>12.1</v>
@@ -5998,28 +5998,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M56">
-        <v>10.7364636</v>
+        <v>10.935287</v>
       </c>
       <c r="N56">
-        <v>12.01686973333334</v>
+        <v>11.81804633333333</v>
       </c>
       <c r="O56">
-        <v>3.004217433333334</v>
+        <v>2.954511583333334</v>
       </c>
       <c r="P56">
-        <v>9.012652300000001</v>
+        <v>8.863534750000001</v>
       </c>
       <c r="Q56">
-        <v>10.0926523</v>
+        <v>9.943534750000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.100030035809823</v>
+        <v>0.1010749305267753</v>
       </c>
       <c r="T56">
-        <v>1.086968398325237</v>
+        <v>1.107911912743835</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.119257716603569</v>
+        <v>2.080725758119867</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6044,22 +6044,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07675121873704888</v>
+        <v>0.07678962100157917</v>
       </c>
       <c r="C57">
-        <v>85.83722434797133</v>
+        <v>83.03684162725028</v>
       </c>
       <c r="D57">
-        <v>218.0022243479713</v>
+        <v>217.8248416272503</v>
       </c>
       <c r="E57">
-        <v>12.36500000000001</v>
+        <v>14.98800000000003</v>
       </c>
       <c r="F57">
-        <v>144.265</v>
+        <v>146.888</v>
       </c>
       <c r="G57">
         <v>12.1</v>
@@ -6080,28 +6080,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M57">
-        <v>10.935287</v>
+        <v>11.1341104</v>
       </c>
       <c r="N57">
-        <v>11.81804633333333</v>
+        <v>11.61922293333333</v>
       </c>
       <c r="O57">
-        <v>2.954511583333334</v>
+        <v>2.904805733333334</v>
       </c>
       <c r="P57">
-        <v>8.863534750000001</v>
+        <v>8.714417200000002</v>
       </c>
       <c r="Q57">
-        <v>9.943534750000001</v>
+        <v>9.794417200000002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1010749305267753</v>
+        <v>0.1021673204581345</v>
       </c>
       <c r="T57">
-        <v>1.107911912743835</v>
+        <v>1.129807405090552</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.080725758119867</v>
+        <v>2.043569941010584</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6126,22 +6126,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07678962100157917</v>
+        <v>0.07682802326610946</v>
       </c>
       <c r="C58">
-        <v>83.03684162725028</v>
+        <v>80.2367473352237</v>
       </c>
       <c r="D58">
-        <v>217.8248416272503</v>
+        <v>217.6477473352237</v>
       </c>
       <c r="E58">
-        <v>14.98800000000003</v>
+        <v>17.61100000000002</v>
       </c>
       <c r="F58">
-        <v>146.888</v>
+        <v>149.511</v>
       </c>
       <c r="G58">
         <v>12.1</v>
@@ -6162,28 +6162,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M58">
-        <v>11.1341104</v>
+        <v>11.3329338</v>
       </c>
       <c r="N58">
-        <v>11.61922293333333</v>
+        <v>11.42039953333333</v>
       </c>
       <c r="O58">
-        <v>2.904805733333334</v>
+        <v>2.855099883333334</v>
       </c>
       <c r="P58">
-        <v>8.714417200000002</v>
+        <v>8.56529965</v>
       </c>
       <c r="Q58">
-        <v>9.794417200000002</v>
+        <v>9.64529965</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1021673204581345</v>
+        <v>0.1033105192235104</v>
       </c>
       <c r="T58">
-        <v>1.129807405090552</v>
+        <v>1.152721292430138</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.043569941010584</v>
+        <v>2.007717836782328</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6208,22 +6208,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07682802326610946</v>
+        <v>0.08304342553063976</v>
       </c>
       <c r="C59">
-        <v>80.2367473352237</v>
+        <v>52.30467725271146</v>
       </c>
       <c r="D59">
-        <v>217.6477473352237</v>
+        <v>192.3386772527115</v>
       </c>
       <c r="E59">
-        <v>17.61100000000002</v>
+        <v>20.23400000000001</v>
       </c>
       <c r="F59">
-        <v>149.511</v>
+        <v>152.134</v>
       </c>
       <c r="G59">
         <v>12.1</v>
@@ -6244,45 +6244,45 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M59">
-        <v>11.3329338</v>
+        <v>13.69206</v>
       </c>
       <c r="N59">
-        <v>11.42039953333333</v>
+        <v>9.061273333333336</v>
       </c>
       <c r="O59">
-        <v>2.855099883333334</v>
+        <v>2.265318333333334</v>
       </c>
       <c r="P59">
-        <v>8.56529965</v>
+        <v>6.795955000000002</v>
       </c>
       <c r="Q59">
-        <v>9.64529965</v>
+        <v>7.875955000000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1033105192235104</v>
+        <v>0.1045081560253328</v>
       </c>
       <c r="T59">
-        <v>1.152721292430138</v>
+        <v>1.176726317262086</v>
       </c>
       <c r="U59">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.007717836782328</v>
+        <v>1.661790361226385</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6290,22 +6290,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08304342553063976</v>
+        <v>0.08318832779517005</v>
       </c>
       <c r="C60">
-        <v>52.30467725271149</v>
+        <v>49.16165875440123</v>
       </c>
       <c r="D60">
-        <v>192.3386772527115</v>
+        <v>191.8186587544012</v>
       </c>
       <c r="E60">
-        <v>20.23399999999998</v>
+        <v>22.857</v>
       </c>
       <c r="F60">
-        <v>152.134</v>
+        <v>154.757</v>
       </c>
       <c r="G60">
         <v>12.1</v>
@@ -6326,28 +6326,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M60">
-        <v>13.69206</v>
+        <v>13.92813</v>
       </c>
       <c r="N60">
-        <v>9.06127333333334</v>
+        <v>8.825203333333338</v>
       </c>
       <c r="O60">
-        <v>2.265318333333335</v>
+        <v>2.206300833333334</v>
       </c>
       <c r="P60">
-        <v>6.795955000000005</v>
+        <v>6.618902500000003</v>
       </c>
       <c r="Q60">
-        <v>7.875955000000005</v>
+        <v>7.698902500000004</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1045081560253328</v>
+        <v>0.1057642141345611</v>
       </c>
       <c r="T60">
-        <v>1.176726317262086</v>
+        <v>1.201902318915105</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.661790361226385</v>
+        <v>1.633624422900514</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6372,22 +6372,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08318832779517005</v>
+        <v>0.08333323005970035</v>
       </c>
       <c r="C61">
-        <v>49.16165875440123</v>
+        <v>46.02144458116985</v>
       </c>
       <c r="D61">
-        <v>191.8186587544012</v>
+        <v>191.3014445811698</v>
       </c>
       <c r="E61">
-        <v>22.857</v>
+        <v>25.47999999999999</v>
       </c>
       <c r="F61">
-        <v>154.757</v>
+        <v>157.38</v>
       </c>
       <c r="G61">
         <v>12.1</v>
@@ -6408,28 +6408,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M61">
-        <v>13.92813</v>
+        <v>14.1642</v>
       </c>
       <c r="N61">
-        <v>8.825203333333338</v>
+        <v>8.589133333333338</v>
       </c>
       <c r="O61">
-        <v>2.206300833333334</v>
+        <v>2.147283333333335</v>
       </c>
       <c r="P61">
-        <v>6.618902500000003</v>
+        <v>6.441850000000004</v>
       </c>
       <c r="Q61">
-        <v>7.698902500000004</v>
+        <v>7.521850000000004</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1057642141345611</v>
+        <v>0.1070830751492509</v>
       </c>
       <c r="T61">
-        <v>1.201902318915105</v>
+        <v>1.228337120650774</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.633624422900514</v>
+        <v>1.606397349185506</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6454,22 +6454,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08333323005970035</v>
+        <v>0.08347813232423065</v>
       </c>
       <c r="C62">
-        <v>46.02144458116985</v>
+        <v>42.88401210952034</v>
       </c>
       <c r="D62">
-        <v>191.3014445811698</v>
+        <v>190.7870121095204</v>
       </c>
       <c r="E62">
-        <v>25.47999999999999</v>
+        <v>28.10300000000001</v>
       </c>
       <c r="F62">
-        <v>157.38</v>
+        <v>160.003</v>
       </c>
       <c r="G62">
         <v>12.1</v>
@@ -6490,28 +6490,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M62">
-        <v>14.1642</v>
+        <v>14.40027</v>
       </c>
       <c r="N62">
-        <v>8.589133333333338</v>
+        <v>8.353063333333337</v>
       </c>
       <c r="O62">
-        <v>2.147283333333335</v>
+        <v>2.088265833333334</v>
       </c>
       <c r="P62">
-        <v>6.441850000000004</v>
+        <v>6.264797500000002</v>
       </c>
       <c r="Q62">
-        <v>7.521850000000004</v>
+        <v>7.344797500000002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1070830751492509</v>
+        <v>0.1084695700621298</v>
       </c>
       <c r="T62">
-        <v>1.228337120650774</v>
+        <v>1.256127553244683</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.606397349185506</v>
+        <v>1.580062966411973</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6536,22 +6536,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08347813232423065</v>
+        <v>0.08362303458876094</v>
       </c>
       <c r="C63">
-        <v>42.88401210952034</v>
+        <v>39.74933895865243</v>
       </c>
       <c r="D63">
-        <v>190.7870121095204</v>
+        <v>190.2753389586524</v>
       </c>
       <c r="E63">
-        <v>28.10300000000001</v>
+        <v>30.726</v>
       </c>
       <c r="F63">
-        <v>160.003</v>
+        <v>162.626</v>
       </c>
       <c r="G63">
         <v>12.1</v>
@@ -6572,28 +6572,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M63">
-        <v>14.40027</v>
+        <v>14.63634</v>
       </c>
       <c r="N63">
-        <v>8.353063333333337</v>
+        <v>8.116993333333337</v>
       </c>
       <c r="O63">
-        <v>2.088265833333334</v>
+        <v>2.029248333333334</v>
       </c>
       <c r="P63">
-        <v>6.264797500000002</v>
+        <v>6.087745000000003</v>
       </c>
       <c r="Q63">
-        <v>7.344797500000002</v>
+        <v>7.167745000000003</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1084695700621298</v>
+        <v>0.1099290383914761</v>
       </c>
       <c r="T63">
-        <v>1.256127553244683</v>
+        <v>1.28538064018564</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.580062966411973</v>
+        <v>1.554578079856941</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6618,22 +6618,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08362303458876094</v>
+        <v>0.08376793685329122</v>
       </c>
       <c r="C64">
-        <v>39.74933895865243</v>
+        <v>36.61740298721642</v>
       </c>
       <c r="D64">
-        <v>190.2753389586524</v>
+        <v>189.7664029872164</v>
       </c>
       <c r="E64">
-        <v>30.726</v>
+        <v>33.34899999999999</v>
       </c>
       <c r="F64">
-        <v>162.626</v>
+        <v>165.249</v>
       </c>
       <c r="G64">
         <v>12.1</v>
@@ -6654,28 +6654,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M64">
-        <v>14.63634</v>
+        <v>14.87241</v>
       </c>
       <c r="N64">
-        <v>8.116993333333337</v>
+        <v>7.880923333333339</v>
       </c>
       <c r="O64">
-        <v>2.029248333333334</v>
+        <v>1.970230833333335</v>
       </c>
       <c r="P64">
-        <v>6.087745000000003</v>
+        <v>5.910692500000004</v>
       </c>
       <c r="Q64">
-        <v>7.167745000000003</v>
+        <v>6.990692500000004</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1099290383914761</v>
+        <v>0.1114673969007871</v>
       </c>
       <c r="T64">
-        <v>1.28538064018564</v>
+        <v>1.316214975069351</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.554578079856941</v>
+        <v>1.529902237319529</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6700,22 +6700,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08376793685329122</v>
+        <v>0.08391283911782152</v>
       </c>
       <c r="C65">
-        <v>36.61740298721642</v>
+        <v>33.48818229011951</v>
       </c>
       <c r="D65">
-        <v>189.7664029872164</v>
+        <v>189.2601822901195</v>
       </c>
       <c r="E65">
-        <v>33.34899999999999</v>
+        <v>35.97200000000001</v>
       </c>
       <c r="F65">
-        <v>165.249</v>
+        <v>167.872</v>
       </c>
       <c r="G65">
         <v>12.1</v>
@@ -6736,28 +6736,28 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M65">
-        <v>14.87241</v>
+        <v>15.10848</v>
       </c>
       <c r="N65">
-        <v>7.880923333333339</v>
+        <v>7.644853333333337</v>
       </c>
       <c r="O65">
-        <v>1.970230833333335</v>
+        <v>1.911213333333334</v>
       </c>
       <c r="P65">
-        <v>5.910692500000004</v>
+        <v>5.733640000000003</v>
       </c>
       <c r="Q65">
-        <v>6.990692500000004</v>
+        <v>6.813640000000003</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1114673969007871</v>
+        <v>0.1130912197717264</v>
       </c>
       <c r="T65">
-        <v>1.316214975069351</v>
+        <v>1.348762328557713</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.529902237319529</v>
+        <v>1.505997514861412</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6782,22 +6782,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08391283911782152</v>
+        <v>0.1143424091280991</v>
       </c>
       <c r="C66">
-        <v>33.48818229011951</v>
+        <v>-37.08973273969013</v>
       </c>
       <c r="D66">
-        <v>189.2601822901195</v>
+        <v>121.3052672603099</v>
       </c>
       <c r="E66">
-        <v>35.97200000000001</v>
+        <v>38.595</v>
       </c>
       <c r="F66">
-        <v>167.872</v>
+        <v>170.495</v>
       </c>
       <c r="G66">
         <v>12.1</v>
@@ -6818,45 +6818,45 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M66">
-        <v>15.10848</v>
+        <v>25.028666</v>
       </c>
       <c r="N66">
-        <v>7.644853333333337</v>
+        <v>-2.275332666666667</v>
       </c>
       <c r="O66">
-        <v>1.911213333333334</v>
+        <v>-0.5688331666666668</v>
       </c>
       <c r="P66">
-        <v>5.733640000000003</v>
+        <v>-1.706499500000001</v>
       </c>
       <c r="Q66">
-        <v>6.813640000000003</v>
+        <v>-0.6264995000000004</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1130912197717264</v>
+        <v>0.1160250666917242</v>
       </c>
       <c r="T66">
-        <v>1.348762328557713</v>
+        <v>1.407567358647398</v>
       </c>
       <c r="U66">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.25</v>
+        <v>0.2272727333263919</v>
       </c>
       <c r="W66">
-        <v>0.0675</v>
+        <v>0.1134363627476857</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.505997514861412</v>
+        <v>0.9090909333055678</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6864,22 +6864,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1143424091280991</v>
+        <v>0.1153524091280991</v>
       </c>
       <c r="C67">
-        <v>-37.08973273969013</v>
+        <v>-41.14136912436334</v>
       </c>
       <c r="D67">
-        <v>121.3052672603099</v>
+        <v>119.8766308756367</v>
       </c>
       <c r="E67">
-        <v>38.595</v>
+        <v>41.21800000000002</v>
       </c>
       <c r="F67">
-        <v>170.495</v>
+        <v>173.118</v>
       </c>
       <c r="G67">
         <v>12.1</v>
@@ -6900,37 +6900,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M67">
-        <v>25.028666</v>
+        <v>25.4137224</v>
       </c>
       <c r="N67">
-        <v>-2.275332666666667</v>
+        <v>-2.660389066666667</v>
       </c>
       <c r="O67">
-        <v>-0.5688331666666668</v>
+        <v>-0.6650972666666668</v>
       </c>
       <c r="P67">
-        <v>-1.706499500000001</v>
+        <v>-1.9952918</v>
       </c>
       <c r="Q67">
-        <v>-0.6264995000000004</v>
+        <v>-0.9152918000000003</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1160250666917242</v>
+        <v>0.1180905098297161</v>
       </c>
       <c r="T67">
-        <v>1.407567358647398</v>
+        <v>1.448966398607616</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2272727333263919</v>
+        <v>0.2238292070638709</v>
       </c>
       <c r="W67">
-        <v>0.1134363627476857</v>
+        <v>0.1139418724030238</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.9090909333055678</v>
+        <v>0.8953168282554835</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6946,22 +6946,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1153524091280991</v>
+        <v>0.1163624091280991</v>
       </c>
       <c r="C68">
-        <v>-41.14136912436334</v>
+        <v>-45.15974653398558</v>
       </c>
       <c r="D68">
-        <v>119.8766308756367</v>
+        <v>118.4812534660144</v>
       </c>
       <c r="E68">
-        <v>41.21800000000002</v>
+        <v>43.84100000000001</v>
       </c>
       <c r="F68">
-        <v>173.118</v>
+        <v>175.741</v>
       </c>
       <c r="G68">
         <v>12.1</v>
@@ -6982,37 +6982,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M68">
-        <v>25.4137224</v>
+        <v>25.7987788</v>
       </c>
       <c r="N68">
-        <v>-2.660389066666667</v>
+        <v>-3.045445466666667</v>
       </c>
       <c r="O68">
-        <v>-0.6650972666666668</v>
+        <v>-0.7613613666666668</v>
       </c>
       <c r="P68">
-        <v>-1.9952918</v>
+        <v>-2.2840841</v>
       </c>
       <c r="Q68">
-        <v>-0.9152918000000003</v>
+        <v>-1.2040841</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1180905098297161</v>
+        <v>0.1202811313397074</v>
       </c>
       <c r="T68">
-        <v>1.448966398607616</v>
+        <v>1.492874471292695</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2238292070638709</v>
+        <v>0.2204884726300818</v>
       </c>
       <c r="W68">
-        <v>0.1139418724030238</v>
+        <v>0.114432292217904</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8953168282554835</v>
+        <v>0.881953890520327</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7028,22 +7028,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1163624091280991</v>
+        <v>0.1173724091280991</v>
       </c>
       <c r="C69">
-        <v>-45.15974653398558</v>
+        <v>-49.14601301969694</v>
       </c>
       <c r="D69">
-        <v>118.4812534660144</v>
+        <v>117.1179869803031</v>
       </c>
       <c r="E69">
-        <v>43.84100000000001</v>
+        <v>46.46400000000003</v>
       </c>
       <c r="F69">
-        <v>175.741</v>
+        <v>178.364</v>
       </c>
       <c r="G69">
         <v>12.1</v>
@@ -7064,37 +7064,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M69">
-        <v>25.7987788</v>
+        <v>26.18383520000001</v>
       </c>
       <c r="N69">
-        <v>-3.045445466666667</v>
+        <v>-3.43050186666667</v>
       </c>
       <c r="O69">
-        <v>-0.7613613666666668</v>
+        <v>-0.8576254666666676</v>
       </c>
       <c r="P69">
-        <v>-2.2840841</v>
+        <v>-2.572876400000003</v>
       </c>
       <c r="Q69">
-        <v>-1.2040841</v>
+        <v>-1.492876400000003</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1202811313397074</v>
+        <v>0.1226086666940733</v>
       </c>
       <c r="T69">
-        <v>1.492874471292695</v>
+        <v>1.539526798520592</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2204884726300818</v>
+        <v>0.217245995091404</v>
       </c>
       <c r="W69">
-        <v>0.114432292217904</v>
+        <v>0.1149082879205819</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.881953890520327</v>
+        <v>0.8689839803656162</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7110,22 +7110,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1173724091280991</v>
+        <v>0.1183824091280991</v>
       </c>
       <c r="C70">
-        <v>-49.14601301969694</v>
+        <v>-53.10126439496671</v>
       </c>
       <c r="D70">
-        <v>117.1179869803031</v>
+        <v>115.7857356050333</v>
       </c>
       <c r="E70">
-        <v>46.46400000000003</v>
+        <v>49.08700000000002</v>
       </c>
       <c r="F70">
-        <v>178.364</v>
+        <v>180.987</v>
       </c>
       <c r="G70">
         <v>12.1</v>
@@ -7146,37 +7146,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M70">
-        <v>26.18383520000001</v>
+        <v>26.5688916</v>
       </c>
       <c r="N70">
-        <v>-3.43050186666667</v>
+        <v>-3.815558266666667</v>
       </c>
       <c r="O70">
-        <v>-0.8576254666666676</v>
+        <v>-0.9538895666666667</v>
       </c>
       <c r="P70">
-        <v>-2.572876400000003</v>
+        <v>-2.8616687</v>
       </c>
       <c r="Q70">
-        <v>-1.492876400000003</v>
+        <v>-1.7816687</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1226086666940733</v>
+        <v>0.1250863656196886</v>
       </c>
       <c r="T70">
-        <v>1.539526798520592</v>
+        <v>1.589188953311579</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.217245995091404</v>
+        <v>0.21409750240892</v>
       </c>
       <c r="W70">
-        <v>0.1149082879205819</v>
+        <v>0.1153704866463705</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8689839803656162</v>
+        <v>0.8563900096356799</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1183824091280991</v>
+        <v>0.1193924091280991</v>
       </c>
       <c r="C71">
-        <v>-53.10126439496671</v>
+        <v>-57.02654717327036</v>
       </c>
       <c r="D71">
-        <v>115.7857356050333</v>
+        <v>114.4834528267297</v>
       </c>
       <c r="E71">
-        <v>49.08700000000002</v>
+        <v>51.71000000000001</v>
       </c>
       <c r="F71">
-        <v>180.987</v>
+        <v>183.61</v>
       </c>
       <c r="G71">
         <v>12.1</v>
@@ -7228,37 +7228,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M71">
-        <v>26.5688916</v>
+        <v>26.953948</v>
       </c>
       <c r="N71">
-        <v>-3.815558266666667</v>
+        <v>-4.200614666666667</v>
       </c>
       <c r="O71">
-        <v>-0.9538895666666667</v>
+        <v>-1.050153666666667</v>
       </c>
       <c r="P71">
-        <v>-2.8616687</v>
+        <v>-3.150461</v>
       </c>
       <c r="Q71">
-        <v>-1.7816687</v>
+        <v>-2.070461</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1250863656196886</v>
+        <v>0.1277292444736782</v>
       </c>
       <c r="T71">
-        <v>1.589188953311579</v>
+        <v>1.642161918421965</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.21409750240892</v>
+        <v>0.2110389666602211</v>
       </c>
       <c r="W71">
-        <v>0.1153704866463705</v>
+        <v>0.1158194796942795</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8563900096356799</v>
+        <v>0.8441558666408844</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7274,22 +7274,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1193924091280991</v>
+        <v>0.1204024091280991</v>
       </c>
       <c r="C72">
-        <v>-57.02654717327036</v>
+        <v>-60.92286130972521</v>
       </c>
       <c r="D72">
-        <v>114.4834528267297</v>
+        <v>113.2101386902748</v>
       </c>
       <c r="E72">
-        <v>51.71000000000001</v>
+        <v>54.33300000000003</v>
       </c>
       <c r="F72">
-        <v>183.61</v>
+        <v>186.233</v>
       </c>
       <c r="G72">
         <v>12.1</v>
@@ -7310,37 +7310,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M72">
-        <v>26.953948</v>
+        <v>27.33900440000001</v>
       </c>
       <c r="N72">
-        <v>-4.200614666666667</v>
+        <v>-4.58567106666667</v>
       </c>
       <c r="O72">
-        <v>-1.050153666666667</v>
+        <v>-1.146417766666668</v>
       </c>
       <c r="P72">
-        <v>-3.150461</v>
+        <v>-3.439253300000003</v>
       </c>
       <c r="Q72">
-        <v>-2.070461</v>
+        <v>-2.359253300000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1277292444736782</v>
+        <v>0.1305543908348396</v>
       </c>
       <c r="T72">
-        <v>1.642161918421965</v>
+        <v>1.698788191470999</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2110389666602211</v>
+        <v>0.2080665868481053</v>
       </c>
       <c r="W72">
-        <v>0.1158194796942795</v>
+        <v>0.1162558250506981</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8441558666408844</v>
+        <v>0.8322663473924212</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7356,22 +7356,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1204024091280992</v>
+        <v>0.1214124091280991</v>
       </c>
       <c r="C73">
-        <v>-60.92286130972521</v>
+        <v>-64.79116276177925</v>
       </c>
       <c r="D73">
-        <v>113.2101386902748</v>
+        <v>111.9648372382208</v>
       </c>
       <c r="E73">
-        <v>54.333</v>
+        <v>56.95599999999999</v>
       </c>
       <c r="F73">
-        <v>186.233</v>
+        <v>188.856</v>
       </c>
       <c r="G73">
         <v>12.1</v>
@@ -7392,37 +7392,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M73">
-        <v>27.3390044</v>
+        <v>27.7240608</v>
       </c>
       <c r="N73">
-        <v>-4.585671066666666</v>
+        <v>-4.970727466666663</v>
       </c>
       <c r="O73">
-        <v>-1.146417766666667</v>
+        <v>-1.242681866666666</v>
       </c>
       <c r="P73">
-        <v>-3.4392533</v>
+        <v>-3.728045599999997</v>
       </c>
       <c r="Q73">
-        <v>-2.3592533</v>
+        <v>-2.648045599999997</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1305543908348395</v>
+        <v>0.1335813333646552</v>
       </c>
       <c r="T73">
-        <v>1.698788191470998</v>
+        <v>1.759459198309248</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2080665868481053</v>
+        <v>0.2051767731418817</v>
       </c>
       <c r="W73">
-        <v>0.1162558250506981</v>
+        <v>0.1166800497027718</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8322663473924212</v>
+        <v>0.8207070925675266</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7438,22 +7438,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1214124091280991</v>
+        <v>0.1224224091280992</v>
       </c>
       <c r="C74">
-        <v>-64.79116276177925</v>
+        <v>-68.63236588273509</v>
       </c>
       <c r="D74">
-        <v>111.9648372382208</v>
+        <v>110.7466341172649</v>
       </c>
       <c r="E74">
-        <v>56.95599999999999</v>
+        <v>59.57900000000001</v>
       </c>
       <c r="F74">
-        <v>188.856</v>
+        <v>191.479</v>
       </c>
       <c r="G74">
         <v>12.1</v>
@@ -7474,37 +7474,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M74">
-        <v>27.7240608</v>
+        <v>28.1091172</v>
       </c>
       <c r="N74">
-        <v>-4.970727466666663</v>
+        <v>-5.355783866666666</v>
       </c>
       <c r="O74">
-        <v>-1.242681866666666</v>
+        <v>-1.338945966666667</v>
       </c>
       <c r="P74">
-        <v>-3.728045599999997</v>
+        <v>-4.0168379</v>
       </c>
       <c r="Q74">
-        <v>-2.648045599999997</v>
+        <v>-2.9368379</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1335813333646552</v>
+        <v>0.1368324938596424</v>
       </c>
       <c r="T74">
-        <v>1.759459198309248</v>
+        <v>1.824624353802183</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2051767731418817</v>
+        <v>0.2023661324139107</v>
       </c>
       <c r="W74">
-        <v>0.1166800497027718</v>
+        <v>0.1170926517616379</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8207070925675266</v>
+        <v>0.8094645296556426</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7520,22 +7520,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1224224091280992</v>
+        <v>0.1645381129412071</v>
       </c>
       <c r="C75">
-        <v>-68.63236588273509</v>
+        <v>-105.8189679846339</v>
       </c>
       <c r="D75">
-        <v>110.7466341172649</v>
+        <v>76.18303201536612</v>
       </c>
       <c r="E75">
-        <v>59.57900000000001</v>
+        <v>62.202</v>
       </c>
       <c r="F75">
-        <v>191.479</v>
+        <v>194.102</v>
       </c>
       <c r="G75">
         <v>12.1</v>
@@ -7556,45 +7556,45 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M75">
-        <v>28.1091172</v>
+        <v>38.9756816</v>
       </c>
       <c r="N75">
-        <v>-5.355783866666666</v>
+        <v>-16.22234826666666</v>
       </c>
       <c r="O75">
-        <v>-1.338945966666667</v>
+        <v>-4.055587066666666</v>
       </c>
       <c r="P75">
-        <v>-4.0168379</v>
+        <v>-12.1667612</v>
       </c>
       <c r="Q75">
-        <v>-2.9368379</v>
+        <v>-11.0867612</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1368324938596424</v>
+        <v>0.1447402967508132</v>
       </c>
       <c r="T75">
-        <v>1.824624353802183</v>
+        <v>1.983125666119786</v>
       </c>
       <c r="U75">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.2023661324139107</v>
+        <v>0.1459457051120136</v>
       </c>
       <c r="W75">
-        <v>0.1170926517616379</v>
+        <v>0.1714941024135077</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.8094645296556426</v>
+        <v>0.5837828204480544</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7602,22 +7602,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1645381129412071</v>
+        <v>0.1660881129412071</v>
       </c>
       <c r="C76">
-        <v>-105.8189679846339</v>
+        <v>-109.307084077726</v>
       </c>
       <c r="D76">
-        <v>76.18303201536612</v>
+        <v>75.317915922274</v>
       </c>
       <c r="E76">
-        <v>62.202</v>
+        <v>64.82500000000002</v>
       </c>
       <c r="F76">
-        <v>194.102</v>
+        <v>196.725</v>
       </c>
       <c r="G76">
         <v>12.1</v>
@@ -7638,37 +7638,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M76">
-        <v>38.9756816</v>
+        <v>39.50238</v>
       </c>
       <c r="N76">
-        <v>-16.22234826666666</v>
+        <v>-16.74904666666666</v>
       </c>
       <c r="O76">
-        <v>-4.055587066666666</v>
+        <v>-4.187261666666666</v>
       </c>
       <c r="P76">
-        <v>-12.1667612</v>
+        <v>-12.561785</v>
       </c>
       <c r="Q76">
-        <v>-11.0867612</v>
+        <v>-11.481785</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1447402967508132</v>
+        <v>0.1486979086208458</v>
       </c>
       <c r="T76">
-        <v>1.983125666119786</v>
+        <v>2.062450692764578</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1459457051120136</v>
+        <v>0.1439997623771867</v>
       </c>
       <c r="W76">
-        <v>0.1714941024135077</v>
+        <v>0.1718848477146609</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5837828204480544</v>
+        <v>0.575999049508747</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7684,22 +7684,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1660881129412071</v>
+        <v>0.1676381129412071</v>
       </c>
       <c r="C77">
-        <v>-109.307084077726</v>
+        <v>-112.7757726862413</v>
       </c>
       <c r="D77">
-        <v>75.317915922274</v>
+        <v>74.47222731375874</v>
       </c>
       <c r="E77">
-        <v>64.82500000000002</v>
+        <v>67.44800000000001</v>
       </c>
       <c r="F77">
-        <v>196.725</v>
+        <v>199.348</v>
       </c>
       <c r="G77">
         <v>12.1</v>
@@ -7720,37 +7720,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M77">
-        <v>39.50238</v>
+        <v>40.0290784</v>
       </c>
       <c r="N77">
-        <v>-16.74904666666666</v>
+        <v>-17.27574506666667</v>
       </c>
       <c r="O77">
-        <v>-4.187261666666666</v>
+        <v>-4.318936266666666</v>
       </c>
       <c r="P77">
-        <v>-12.561785</v>
+        <v>-12.9568088</v>
       </c>
       <c r="Q77">
-        <v>-11.481785</v>
+        <v>-11.8768088</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1486979086208458</v>
+        <v>0.1529853214800476</v>
       </c>
       <c r="T77">
-        <v>2.062450692764578</v>
+        <v>2.148386138296436</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1439997623771867</v>
+        <v>0.1421050286616974</v>
       </c>
       <c r="W77">
-        <v>0.1718848477146609</v>
+        <v>0.1722653102447312</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.575999049508747</v>
+        <v>0.5684201146467898</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7766,22 +7766,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1676381129412071</v>
+        <v>0.1691881129412071</v>
       </c>
       <c r="C78">
-        <v>-112.7757726862413</v>
+        <v>-116.2256809540156</v>
       </c>
       <c r="D78">
-        <v>74.47222731375874</v>
+        <v>73.64531904598444</v>
       </c>
       <c r="E78">
-        <v>67.44800000000001</v>
+        <v>70.071</v>
       </c>
       <c r="F78">
-        <v>199.348</v>
+        <v>201.971</v>
       </c>
       <c r="G78">
         <v>12.1</v>
@@ -7802,37 +7802,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M78">
-        <v>40.0290784</v>
+        <v>40.5557768</v>
       </c>
       <c r="N78">
-        <v>-17.27574506666667</v>
+        <v>-17.80244346666667</v>
       </c>
       <c r="O78">
-        <v>-4.318936266666666</v>
+        <v>-4.450610866666667</v>
       </c>
       <c r="P78">
-        <v>-12.9568088</v>
+        <v>-13.3518326</v>
       </c>
       <c r="Q78">
-        <v>-11.8768088</v>
+        <v>-12.2718326</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1529853214800476</v>
+        <v>0.1576455528487454</v>
       </c>
       <c r="T78">
-        <v>2.148386138296436</v>
+        <v>2.241794231265846</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1421050286616974</v>
+        <v>0.1402595088089481</v>
       </c>
       <c r="W78">
-        <v>0.1722653102447312</v>
+        <v>0.1726358906311632</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5684201146467898</v>
+        <v>0.5610380352357924</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7848,22 +7848,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1691881129412071</v>
+        <v>0.1707381129412071</v>
       </c>
       <c r="C79">
-        <v>-116.2256809540156</v>
+        <v>-119.6574275980732</v>
       </c>
       <c r="D79">
-        <v>73.64531904598444</v>
+        <v>72.83657240192683</v>
       </c>
       <c r="E79">
-        <v>70.071</v>
+        <v>72.69400000000002</v>
       </c>
       <c r="F79">
-        <v>201.971</v>
+        <v>204.594</v>
       </c>
       <c r="G79">
         <v>12.1</v>
@@ -7884,37 +7884,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M79">
-        <v>40.5557768</v>
+        <v>41.0824752</v>
       </c>
       <c r="N79">
-        <v>-17.80244346666667</v>
+        <v>-18.32914186666667</v>
       </c>
       <c r="O79">
-        <v>-4.450610866666667</v>
+        <v>-4.582285466666667</v>
       </c>
       <c r="P79">
-        <v>-13.3518326</v>
+        <v>-13.7468564</v>
       </c>
       <c r="Q79">
-        <v>-12.2718326</v>
+        <v>-12.6668564</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1576455528487454</v>
+        <v>0.1627294416145975</v>
       </c>
       <c r="T79">
-        <v>2.241794231265846</v>
+        <v>2.343693969050657</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1402595088089481</v>
+        <v>0.1384613099780642</v>
       </c>
       <c r="W79">
-        <v>0.1726358906311632</v>
+        <v>0.1729969689564047</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5610380352357924</v>
+        <v>0.5538452399122566</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7930,22 +7930,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1707381129412071</v>
+        <v>0.1722881129412071</v>
       </c>
       <c r="C80">
-        <v>-119.6574275980732</v>
+        <v>-123.0716044525374</v>
       </c>
       <c r="D80">
-        <v>72.83657240192683</v>
+        <v>72.04539554746263</v>
       </c>
       <c r="E80">
-        <v>72.69400000000002</v>
+        <v>75.31700000000001</v>
       </c>
       <c r="F80">
-        <v>204.594</v>
+        <v>207.217</v>
       </c>
       <c r="G80">
         <v>12.1</v>
@@ -7966,37 +7966,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M80">
-        <v>41.0824752</v>
+        <v>41.60917360000001</v>
       </c>
       <c r="N80">
-        <v>-18.32914186666667</v>
+        <v>-18.85584026666667</v>
       </c>
       <c r="O80">
-        <v>-4.582285466666667</v>
+        <v>-4.713960066666667</v>
       </c>
       <c r="P80">
-        <v>-13.7468564</v>
+        <v>-14.1418802</v>
       </c>
       <c r="Q80">
-        <v>-12.6668564</v>
+        <v>-13.0618802</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1627294416145975</v>
+        <v>0.1682975102629116</v>
       </c>
       <c r="T80">
-        <v>2.343693969050657</v>
+        <v>2.455298443767355</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1384613099780642</v>
+        <v>0.1367086351682152</v>
       </c>
       <c r="W80">
-        <v>0.1729969689564047</v>
+        <v>0.1733489060582224</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5538452399122566</v>
+        <v>0.546834540672861</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8012,22 +8012,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1722881129412071</v>
+        <v>0.1738381129412072</v>
       </c>
       <c r="C81">
-        <v>-123.0716044525374</v>
+        <v>-126.4687779129997</v>
       </c>
       <c r="D81">
-        <v>72.04539554746263</v>
+        <v>71.27122208700037</v>
       </c>
       <c r="E81">
-        <v>75.31700000000001</v>
+        <v>77.94000000000003</v>
       </c>
       <c r="F81">
-        <v>207.217</v>
+        <v>209.84</v>
       </c>
       <c r="G81">
         <v>12.1</v>
@@ -8048,37 +8048,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M81">
-        <v>41.60917360000001</v>
+        <v>42.13587200000001</v>
       </c>
       <c r="N81">
-        <v>-18.85584026666667</v>
+        <v>-19.38253866666667</v>
       </c>
       <c r="O81">
-        <v>-4.713960066666667</v>
+        <v>-4.845634666666667</v>
       </c>
       <c r="P81">
-        <v>-14.1418802</v>
+        <v>-14.536904</v>
       </c>
       <c r="Q81">
-        <v>-13.0618802</v>
+        <v>-13.456904</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1682975102629116</v>
+        <v>0.1744223857760572</v>
       </c>
       <c r="T81">
-        <v>2.455298443767355</v>
+        <v>2.578063365955723</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1367086351682152</v>
+        <v>0.1349997772286126</v>
       </c>
       <c r="W81">
-        <v>0.1733489060582224</v>
+        <v>0.1736920447324946</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.546834540672861</v>
+        <v>0.5399991089144502</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8094,22 +8094,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1738381129412072</v>
+        <v>0.1753881129412071</v>
       </c>
       <c r="C82">
-        <v>-126.4687779129997</v>
+        <v>-129.8494902887549</v>
       </c>
       <c r="D82">
-        <v>71.27122208700037</v>
+        <v>70.51350971124512</v>
       </c>
       <c r="E82">
-        <v>77.94000000000003</v>
+        <v>80.56300000000002</v>
       </c>
       <c r="F82">
-        <v>209.84</v>
+        <v>212.463</v>
       </c>
       <c r="G82">
         <v>12.1</v>
@@ -8130,37 +8130,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M82">
-        <v>42.13587200000001</v>
+        <v>42.66257040000001</v>
       </c>
       <c r="N82">
-        <v>-19.38253866666667</v>
+        <v>-19.90923706666667</v>
       </c>
       <c r="O82">
-        <v>-4.845634666666667</v>
+        <v>-4.977309266666667</v>
       </c>
       <c r="P82">
-        <v>-14.536904</v>
+        <v>-14.9319278</v>
       </c>
       <c r="Q82">
-        <v>-13.456904</v>
+        <v>-13.8519278</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1744223857760572</v>
+        <v>0.1811919850274286</v>
       </c>
       <c r="T82">
-        <v>2.578063365955723</v>
+        <v>2.71375091153234</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1349997772286126</v>
+        <v>0.1333331133122099</v>
       </c>
       <c r="W82">
-        <v>0.1736920447324946</v>
+        <v>0.1740267108469082</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5399991089144502</v>
+        <v>0.5333324532488397</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8176,22 +8176,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1753881129412071</v>
+        <v>0.1769381129412071</v>
       </c>
       <c r="C83">
-        <v>-129.8494902887549</v>
+        <v>-133.214261069687</v>
       </c>
       <c r="D83">
-        <v>70.51350971124512</v>
+        <v>69.77173893031301</v>
       </c>
       <c r="E83">
-        <v>80.56300000000002</v>
+        <v>83.18600000000001</v>
       </c>
       <c r="F83">
-        <v>212.463</v>
+        <v>215.086</v>
       </c>
       <c r="G83">
         <v>12.1</v>
@@ -8212,37 +8212,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M83">
-        <v>42.66257040000001</v>
+        <v>43.1892688</v>
       </c>
       <c r="N83">
-        <v>-19.90923706666667</v>
+        <v>-20.43593546666666</v>
       </c>
       <c r="O83">
-        <v>-4.977309266666667</v>
+        <v>-5.108983866666666</v>
       </c>
       <c r="P83">
-        <v>-14.9319278</v>
+        <v>-15.3269516</v>
       </c>
       <c r="Q83">
-        <v>-13.8519278</v>
+        <v>-14.2469516</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1811919850274286</v>
+        <v>0.1887137619733969</v>
       </c>
       <c r="T83">
-        <v>2.71375091153234</v>
+        <v>2.864514851061915</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1333331133122099</v>
+        <v>0.1317070997352318</v>
       </c>
       <c r="W83">
-        <v>0.1740267108469082</v>
+        <v>0.1743532143731655</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5333324532488397</v>
+        <v>0.5268283989409271</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8258,22 +8258,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1769381129412071</v>
+        <v>0.1784881129412071</v>
       </c>
       <c r="C84">
-        <v>-133.214261069687</v>
+        <v>-136.5635881140246</v>
       </c>
       <c r="D84">
-        <v>69.77173893031301</v>
+        <v>69.04541188597538</v>
       </c>
       <c r="E84">
-        <v>83.18600000000001</v>
+        <v>85.80900000000003</v>
       </c>
       <c r="F84">
-        <v>215.086</v>
+        <v>217.709</v>
       </c>
       <c r="G84">
         <v>12.1</v>
@@ -8294,37 +8294,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M84">
-        <v>43.1892688</v>
+        <v>43.71596720000001</v>
       </c>
       <c r="N84">
-        <v>-20.43593546666666</v>
+        <v>-20.96263386666667</v>
       </c>
       <c r="O84">
-        <v>-5.108983866666666</v>
+        <v>-5.240658466666668</v>
       </c>
       <c r="P84">
-        <v>-15.3269516</v>
+        <v>-15.7219754</v>
       </c>
       <c r="Q84">
-        <v>-14.2469516</v>
+        <v>-14.6419754</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1887137619733969</v>
+        <v>0.197120453854185</v>
       </c>
       <c r="T84">
-        <v>2.864514851061915</v>
+        <v>3.033015724653792</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1317070997352318</v>
+        <v>0.1301202672083012</v>
       </c>
       <c r="W84">
-        <v>0.1743532143731655</v>
+        <v>0.1746718503445731</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5268283989409271</v>
+        <v>0.520481068833205</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8340,22 +8340,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1784881129412071</v>
+        <v>0.1800381129412071</v>
       </c>
       <c r="C85">
-        <v>-136.5635881140246</v>
+        <v>-139.8979487626735</v>
       </c>
       <c r="D85">
-        <v>69.04541188597538</v>
+        <v>68.33405123732653</v>
       </c>
       <c r="E85">
-        <v>85.80900000000003</v>
+        <v>88.43200000000002</v>
       </c>
       <c r="F85">
-        <v>217.709</v>
+        <v>220.332</v>
       </c>
       <c r="G85">
         <v>12.1</v>
@@ -8376,37 +8376,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M85">
-        <v>43.71596720000001</v>
+        <v>44.2426656</v>
       </c>
       <c r="N85">
-        <v>-20.96263386666667</v>
+        <v>-21.48933226666666</v>
       </c>
       <c r="O85">
-        <v>-5.240658466666668</v>
+        <v>-5.372333066666666</v>
       </c>
       <c r="P85">
-        <v>-15.7219754</v>
+        <v>-16.1169992</v>
       </c>
       <c r="Q85">
-        <v>-14.6419754</v>
+        <v>-15.0369992</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.197120453854185</v>
+        <v>0.2065779822200716</v>
       </c>
       <c r="T85">
-        <v>3.033015724653792</v>
+        <v>3.222579207444655</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1301202672083012</v>
+        <v>0.1285712164082025</v>
       </c>
       <c r="W85">
-        <v>0.1746718503445731</v>
+        <v>0.174982899745233</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.520481068833205</v>
+        <v>0.5142848656328098</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8422,22 +8422,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1800381129412071</v>
+        <v>0.1815881129412071</v>
       </c>
       <c r="C86">
-        <v>-139.8979487626734</v>
+        <v>-143.2178008853668</v>
       </c>
       <c r="D86">
-        <v>68.33405123732656</v>
+        <v>67.63719911463326</v>
       </c>
       <c r="E86">
-        <v>88.43199999999999</v>
+        <v>91.05500000000001</v>
       </c>
       <c r="F86">
-        <v>220.332</v>
+        <v>222.955</v>
       </c>
       <c r="G86">
         <v>12.1</v>
@@ -8458,37 +8458,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M86">
-        <v>44.2426656</v>
+        <v>44.769364</v>
       </c>
       <c r="N86">
-        <v>-21.48933226666666</v>
+        <v>-22.01603066666667</v>
       </c>
       <c r="O86">
-        <v>-5.372333066666666</v>
+        <v>-5.504007666666666</v>
       </c>
       <c r="P86">
-        <v>-16.1169992</v>
+        <v>-16.512023</v>
       </c>
       <c r="Q86">
-        <v>-15.0369992</v>
+        <v>-15.432023</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2065779822200715</v>
+        <v>0.2172965143680762</v>
       </c>
       <c r="T86">
-        <v>3.222579207444653</v>
+        <v>3.437417821274297</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1285712164082025</v>
+        <v>0.1270586138622236</v>
       </c>
       <c r="W86">
-        <v>0.174982899745233</v>
+        <v>0.1752866303364655</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5142848656328098</v>
+        <v>0.5082344554488945</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8504,22 +8504,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1815881129412071</v>
+        <v>0.1831381129412071</v>
       </c>
       <c r="C87">
-        <v>-143.2178008853668</v>
+        <v>-146.5235838634519</v>
       </c>
       <c r="D87">
-        <v>67.63719911463326</v>
+        <v>66.95441613654813</v>
       </c>
       <c r="E87">
-        <v>91.05500000000001</v>
+        <v>93.678</v>
       </c>
       <c r="F87">
-        <v>222.955</v>
+        <v>225.578</v>
       </c>
       <c r="G87">
         <v>12.1</v>
@@ -8540,37 +8540,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M87">
-        <v>44.769364</v>
+        <v>45.2960624</v>
       </c>
       <c r="N87">
-        <v>-22.01603066666667</v>
+        <v>-22.54272906666667</v>
       </c>
       <c r="O87">
-        <v>-5.504007666666666</v>
+        <v>-5.635682266666667</v>
       </c>
       <c r="P87">
-        <v>-16.512023</v>
+        <v>-16.9070468</v>
       </c>
       <c r="Q87">
-        <v>-15.432023</v>
+        <v>-15.8270468</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2172965143680762</v>
+        <v>0.2295462653943674</v>
       </c>
       <c r="T87">
-        <v>3.437417821274297</v>
+        <v>3.682947665651032</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1270586138622236</v>
+        <v>0.1255811881196396</v>
       </c>
       <c r="W87">
-        <v>0.1752866303364655</v>
+        <v>0.1755832974255764</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5082344554488945</v>
+        <v>0.5023247524785583</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8586,22 +8586,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1831381129412071</v>
+        <v>0.2156004182683636</v>
       </c>
       <c r="C88">
-        <v>-146.5235838634519</v>
+        <v>-160.8316036442777</v>
       </c>
       <c r="D88">
-        <v>66.95441613654813</v>
+        <v>55.26939635572232</v>
       </c>
       <c r="E88">
-        <v>93.678</v>
+        <v>96.30100000000002</v>
       </c>
       <c r="F88">
-        <v>225.578</v>
+        <v>228.201</v>
       </c>
       <c r="G88">
         <v>12.1</v>
@@ -8622,45 +8622,45 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M88">
-        <v>45.2960624</v>
+        <v>53.80979580000001</v>
       </c>
       <c r="N88">
-        <v>-22.54272906666667</v>
+        <v>-31.05646246666667</v>
       </c>
       <c r="O88">
-        <v>-5.635682266666667</v>
+        <v>-7.764115616666668</v>
       </c>
       <c r="P88">
-        <v>-16.9070468</v>
+        <v>-23.29234685</v>
       </c>
       <c r="Q88">
-        <v>-15.8270468</v>
+        <v>-22.21234685</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2295462653943674</v>
+        <v>0.247236788325907</v>
       </c>
       <c r="T88">
-        <v>3.682947665651032</v>
+        <v>4.037530492110246</v>
       </c>
       <c r="U88">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1255811881196396</v>
+        <v>0.1057118550398464</v>
       </c>
       <c r="W88">
-        <v>0.1755832974255764</v>
+        <v>0.2108731445816042</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.5023247524785583</v>
+        <v>0.4228474201593854</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8668,22 +8668,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2156004182683636</v>
+        <v>0.2175004182683636</v>
       </c>
       <c r="C89">
-        <v>-160.8316036442777</v>
+        <v>-164.0134539805028</v>
       </c>
       <c r="D89">
-        <v>55.26939635572232</v>
+        <v>54.71054601949726</v>
       </c>
       <c r="E89">
-        <v>96.30100000000002</v>
+        <v>98.92400000000001</v>
       </c>
       <c r="F89">
-        <v>228.201</v>
+        <v>230.824</v>
       </c>
       <c r="G89">
         <v>12.1</v>
@@ -8704,37 +8704,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M89">
-        <v>53.80979580000001</v>
+        <v>54.4282992</v>
       </c>
       <c r="N89">
-        <v>-31.05646246666667</v>
+        <v>-31.67496586666667</v>
       </c>
       <c r="O89">
-        <v>-7.764115616666668</v>
+        <v>-7.918741466666667</v>
       </c>
       <c r="P89">
-        <v>-23.29234685</v>
+        <v>-23.7562244</v>
       </c>
       <c r="Q89">
-        <v>-22.21234685</v>
+        <v>-22.6762244</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.247236788325907</v>
+        <v>0.2640231873530659</v>
       </c>
       <c r="T89">
-        <v>4.037530492110246</v>
+        <v>4.373991366452768</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1057118550398464</v>
+        <v>0.1045105839598481</v>
       </c>
       <c r="W89">
-        <v>0.2108731445816042</v>
+        <v>0.2111564043022678</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4228474201593854</v>
+        <v>0.4180423358393924</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8750,22 +8750,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2175004182683636</v>
+        <v>0.2194004182683636</v>
       </c>
       <c r="C90">
-        <v>-164.0134539805028</v>
+        <v>-167.1841159410648</v>
       </c>
       <c r="D90">
-        <v>54.71054601949726</v>
+        <v>54.1628840589352</v>
       </c>
       <c r="E90">
-        <v>98.92400000000001</v>
+        <v>101.547</v>
       </c>
       <c r="F90">
-        <v>230.824</v>
+        <v>233.447</v>
       </c>
       <c r="G90">
         <v>12.1</v>
@@ -8786,37 +8786,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M90">
-        <v>54.4282992</v>
+        <v>55.0468026</v>
       </c>
       <c r="N90">
-        <v>-31.67496586666667</v>
+        <v>-32.29346926666666</v>
       </c>
       <c r="O90">
-        <v>-7.918741466666667</v>
+        <v>-8.073367316666666</v>
       </c>
       <c r="P90">
-        <v>-23.7562244</v>
+        <v>-24.22010195</v>
       </c>
       <c r="Q90">
-        <v>-22.6762244</v>
+        <v>-23.14010194999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2640231873530659</v>
+        <v>0.2838616589306174</v>
       </c>
       <c r="T90">
-        <v>4.373991366452768</v>
+        <v>4.771626945221201</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1045105839598481</v>
+        <v>0.1033363077355802</v>
       </c>
       <c r="W90">
-        <v>0.2111564043022678</v>
+        <v>0.2114332986359502</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4180423358393924</v>
+        <v>0.4133452309423207</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8832,22 +8832,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2194004182683636</v>
+        <v>0.2213004182683636</v>
       </c>
       <c r="C91">
-        <v>-167.1841159410648</v>
+        <v>-170.3439221886383</v>
       </c>
       <c r="D91">
-        <v>54.1628840589352</v>
+        <v>53.62607781136171</v>
       </c>
       <c r="E91">
-        <v>101.547</v>
+        <v>104.17</v>
       </c>
       <c r="F91">
-        <v>233.447</v>
+        <v>236.07</v>
       </c>
       <c r="G91">
         <v>12.1</v>
@@ -8868,37 +8868,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M91">
-        <v>55.0468026</v>
+        <v>55.66530600000001</v>
       </c>
       <c r="N91">
-        <v>-32.29346926666666</v>
+        <v>-32.91197266666667</v>
       </c>
       <c r="O91">
-        <v>-8.073367316666666</v>
+        <v>-8.227993166666668</v>
       </c>
       <c r="P91">
-        <v>-24.22010195</v>
+        <v>-24.6839795</v>
       </c>
       <c r="Q91">
-        <v>-23.14010194999999</v>
+        <v>-23.6039795</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2838616589306174</v>
+        <v>0.3076678248236791</v>
       </c>
       <c r="T91">
-        <v>4.771626945221201</v>
+        <v>5.248789639743322</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1033363077355802</v>
+        <v>0.1021881265385182</v>
       </c>
       <c r="W91">
-        <v>0.2114332986359502</v>
+        <v>0.2117040397622174</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4133452309423207</v>
+        <v>0.4087525061540725</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8914,22 +8914,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2213004182683636</v>
+        <v>0.2232004182683636</v>
       </c>
       <c r="C92">
-        <v>-170.3439221886383</v>
+        <v>-173.4931923272935</v>
       </c>
       <c r="D92">
-        <v>53.62607781136171</v>
+        <v>53.09980767270654</v>
       </c>
       <c r="E92">
-        <v>104.17</v>
+        <v>106.793</v>
       </c>
       <c r="F92">
-        <v>236.07</v>
+        <v>238.693</v>
       </c>
       <c r="G92">
         <v>12.1</v>
@@ -8950,37 +8950,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M92">
-        <v>55.66530600000001</v>
+        <v>56.2838094</v>
       </c>
       <c r="N92">
-        <v>-32.91197266666667</v>
+        <v>-33.53047606666667</v>
       </c>
       <c r="O92">
-        <v>-8.227993166666668</v>
+        <v>-8.382619016666666</v>
       </c>
       <c r="P92">
-        <v>-24.6839795</v>
+        <v>-25.14785705</v>
       </c>
       <c r="Q92">
-        <v>-23.6039795</v>
+        <v>-24.06785705</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3076678248236791</v>
+        <v>0.336764249804088</v>
       </c>
       <c r="T92">
-        <v>5.248789639743322</v>
+        <v>5.831988488603692</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1021881265385182</v>
+        <v>0.1010651800930399</v>
       </c>
       <c r="W92">
-        <v>0.2117040397622174</v>
+        <v>0.2119688305340612</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4087525061540725</v>
+        <v>0.4042607203721598</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8996,22 +8996,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2232004182683636</v>
+        <v>0.2251004182683636</v>
       </c>
       <c r="C93">
-        <v>-173.4931923272935</v>
+        <v>-176.6322335370351</v>
       </c>
       <c r="D93">
-        <v>53.09980767270654</v>
+        <v>52.58376646296488</v>
       </c>
       <c r="E93">
-        <v>106.793</v>
+        <v>109.416</v>
       </c>
       <c r="F93">
-        <v>238.693</v>
+        <v>241.316</v>
       </c>
       <c r="G93">
         <v>12.1</v>
@@ -9032,37 +9032,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M93">
-        <v>56.2838094</v>
+        <v>56.90231280000001</v>
       </c>
       <c r="N93">
-        <v>-33.53047606666667</v>
+        <v>-34.14897946666667</v>
       </c>
       <c r="O93">
-        <v>-8.382619016666666</v>
+        <v>-8.537244866666668</v>
       </c>
       <c r="P93">
-        <v>-25.14785705</v>
+        <v>-25.61173460000001</v>
       </c>
       <c r="Q93">
-        <v>-24.06785705</v>
+        <v>-24.53173460000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.336764249804088</v>
+        <v>0.373134781029599</v>
       </c>
       <c r="T93">
-        <v>5.831988488603692</v>
+        <v>6.560987049679155</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1010651800930399</v>
+        <v>0.09996664552681123</v>
       </c>
       <c r="W93">
-        <v>0.2119688305340612</v>
+        <v>0.2122278649847779</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4042607203721598</v>
+        <v>0.3998665821072449</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9078,22 +9078,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2251004182683636</v>
+        <v>0.2270004182683636</v>
       </c>
       <c r="C94">
-        <v>-176.6322335370351</v>
+        <v>-179.7613411716977</v>
       </c>
       <c r="D94">
-        <v>52.58376646296488</v>
+        <v>52.07765882830235</v>
       </c>
       <c r="E94">
-        <v>109.416</v>
+        <v>112.039</v>
       </c>
       <c r="F94">
-        <v>241.316</v>
+        <v>243.939</v>
       </c>
       <c r="G94">
         <v>12.1</v>
@@ -9114,37 +9114,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M94">
-        <v>56.90231280000001</v>
+        <v>57.52081620000001</v>
       </c>
       <c r="N94">
-        <v>-34.14897946666667</v>
+        <v>-34.76748286666667</v>
       </c>
       <c r="O94">
-        <v>-8.537244866666668</v>
+        <v>-8.691870716666667</v>
       </c>
       <c r="P94">
-        <v>-25.61173460000001</v>
+        <v>-26.07561215</v>
       </c>
       <c r="Q94">
-        <v>-24.53173460000001</v>
+        <v>-24.99561215</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.373134781029599</v>
+        <v>0.4198968926052561</v>
       </c>
       <c r="T94">
-        <v>6.560987049679155</v>
+        <v>7.498270913919035</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09996664552681123</v>
+        <v>0.09889173535985628</v>
       </c>
       <c r="W94">
-        <v>0.2122278649847779</v>
+        <v>0.2124813288021459</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3998665821072449</v>
+        <v>0.3955669414394251</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9160,22 +9160,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2270004182683636</v>
+        <v>0.2289004182683636</v>
       </c>
       <c r="C95">
-        <v>-179.7613411716977</v>
+        <v>-182.8807993226416</v>
       </c>
       <c r="D95">
-        <v>52.07765882830235</v>
+        <v>51.58120067735839</v>
       </c>
       <c r="E95">
-        <v>112.039</v>
+        <v>114.662</v>
       </c>
       <c r="F95">
-        <v>243.939</v>
+        <v>246.562</v>
       </c>
       <c r="G95">
         <v>12.1</v>
@@ -9196,37 +9196,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M95">
-        <v>57.52081620000001</v>
+        <v>58.13931960000001</v>
       </c>
       <c r="N95">
-        <v>-34.76748286666667</v>
+        <v>-35.38598626666667</v>
       </c>
       <c r="O95">
-        <v>-8.691870716666667</v>
+        <v>-8.846496566666668</v>
       </c>
       <c r="P95">
-        <v>-26.07561215</v>
+        <v>-26.5394897</v>
       </c>
       <c r="Q95">
-        <v>-24.99561215</v>
+        <v>-25.45948970000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4198968926052561</v>
+        <v>0.4822463747061322</v>
       </c>
       <c r="T95">
-        <v>7.498270913919035</v>
+        <v>8.747982732905543</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09889173535985628</v>
+        <v>0.09783969562198547</v>
       </c>
       <c r="W95">
-        <v>0.2124813288021459</v>
+        <v>0.2127293997723358</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3955669414394251</v>
+        <v>0.3913587824879419</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9242,22 +9242,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2289004182683636</v>
+        <v>0.2308004182683636</v>
       </c>
       <c r="C96">
-        <v>-182.8807993226416</v>
+        <v>-185.9908813505121</v>
       </c>
       <c r="D96">
-        <v>51.58120067735839</v>
+        <v>51.0941186494879</v>
       </c>
       <c r="E96">
-        <v>114.662</v>
+        <v>117.285</v>
       </c>
       <c r="F96">
-        <v>246.562</v>
+        <v>249.185</v>
       </c>
       <c r="G96">
         <v>12.1</v>
@@ -9278,37 +9278,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M96">
-        <v>58.13931960000001</v>
+        <v>58.75782300000001</v>
       </c>
       <c r="N96">
-        <v>-35.38598626666667</v>
+        <v>-36.00448966666667</v>
       </c>
       <c r="O96">
-        <v>-8.846496566666668</v>
+        <v>-9.001122416666668</v>
       </c>
       <c r="P96">
-        <v>-26.5394897</v>
+        <v>-27.00336725</v>
       </c>
       <c r="Q96">
-        <v>-25.45948970000001</v>
+        <v>-25.92336725000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4822463747061322</v>
+        <v>0.5695356496473589</v>
       </c>
       <c r="T96">
-        <v>8.747982732905543</v>
+        <v>10.49757927948666</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09783969562198547</v>
+        <v>0.09680980408912246</v>
       </c>
       <c r="W96">
-        <v>0.2127293997723358</v>
+        <v>0.2129722481957849</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3913587824879419</v>
+        <v>0.3872392163564898</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9324,22 +9324,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2308004182683636</v>
+        <v>0.2327004182683636</v>
       </c>
       <c r="C97">
-        <v>-185.9908813505121</v>
+        <v>-189.0918503871508</v>
       </c>
       <c r="D97">
-        <v>51.0941186494879</v>
+        <v>50.61614961284926</v>
       </c>
       <c r="E97">
-        <v>117.285</v>
+        <v>119.908</v>
       </c>
       <c r="F97">
-        <v>249.185</v>
+        <v>251.808</v>
       </c>
       <c r="G97">
         <v>12.1</v>
@@ -9360,37 +9360,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M97">
-        <v>58.75782300000001</v>
+        <v>59.37632640000001</v>
       </c>
       <c r="N97">
-        <v>-36.00448966666667</v>
+        <v>-36.62299306666667</v>
       </c>
       <c r="O97">
-        <v>-9.001122416666668</v>
+        <v>-9.155748266666668</v>
       </c>
       <c r="P97">
-        <v>-27.00336725</v>
+        <v>-27.4672448</v>
       </c>
       <c r="Q97">
-        <v>-25.92336725000001</v>
+        <v>-26.3872448</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5695356496473589</v>
+        <v>0.7004695620591989</v>
       </c>
       <c r="T97">
-        <v>10.49757927948666</v>
+        <v>13.12197409935833</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09680980408912246</v>
+        <v>0.09580136862986076</v>
       </c>
       <c r="W97">
-        <v>0.2129722481957849</v>
+        <v>0.2132100372770789</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3872392163564898</v>
+        <v>0.3832054745194431</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9406,22 +9406,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2327004182683636</v>
+        <v>0.2346004182683636</v>
       </c>
       <c r="C98">
-        <v>-189.0918503871508</v>
+        <v>-192.1839598095975</v>
       </c>
       <c r="D98">
-        <v>50.61614961284923</v>
+        <v>50.14704019040248</v>
       </c>
       <c r="E98">
-        <v>119.908</v>
+        <v>122.531</v>
       </c>
       <c r="F98">
-        <v>251.808</v>
+        <v>254.431</v>
       </c>
       <c r="G98">
         <v>12.1</v>
@@ -9442,37 +9442,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M98">
-        <v>59.3763264</v>
+        <v>59.99482980000001</v>
       </c>
       <c r="N98">
-        <v>-36.62299306666667</v>
+        <v>-37.24149646666667</v>
       </c>
       <c r="O98">
-        <v>-9.155748266666667</v>
+        <v>-9.310374116666667</v>
       </c>
       <c r="P98">
-        <v>-27.4672448</v>
+        <v>-27.93112235</v>
       </c>
       <c r="Q98">
-        <v>-26.3872448</v>
+        <v>-26.85112235</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7004695620591971</v>
+        <v>0.9186927494122629</v>
       </c>
       <c r="T98">
-        <v>13.12197409935829</v>
+        <v>17.49596546581106</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09580136862986077</v>
+        <v>0.09481372565429519</v>
       </c>
       <c r="W98">
-        <v>0.2132100372770789</v>
+        <v>0.2134429234907172</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3832054745194431</v>
+        <v>0.3792549026171808</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9488,22 +9488,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2346004182683636</v>
+        <v>0.2365004182683636</v>
       </c>
       <c r="C99">
-        <v>-192.1839598095975</v>
+        <v>-195.267453687976</v>
       </c>
       <c r="D99">
-        <v>50.14704019040248</v>
+        <v>49.68654631202402</v>
       </c>
       <c r="E99">
-        <v>122.531</v>
+        <v>125.154</v>
       </c>
       <c r="F99">
-        <v>254.431</v>
+        <v>257.054</v>
       </c>
       <c r="G99">
         <v>12.1</v>
@@ -9524,37 +9524,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M99">
-        <v>59.99482980000001</v>
+        <v>60.61333320000001</v>
       </c>
       <c r="N99">
-        <v>-37.24149646666667</v>
+        <v>-37.85999986666667</v>
       </c>
       <c r="O99">
-        <v>-9.310374116666667</v>
+        <v>-9.464999966666667</v>
       </c>
       <c r="P99">
-        <v>-27.93112235</v>
+        <v>-28.3949999</v>
       </c>
       <c r="Q99">
-        <v>-26.85112235</v>
+        <v>-27.3149999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9186927494122629</v>
+        <v>1.355139124118394</v>
       </c>
       <c r="T99">
-        <v>17.49596546581106</v>
+        <v>26.24394819871658</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09481372565429519</v>
+        <v>0.09384623865782279</v>
       </c>
       <c r="W99">
-        <v>0.2134429234907172</v>
+        <v>0.2136710569244854</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3792549026171808</v>
+        <v>0.3753849546312912</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9570,22 +9570,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2365004182683636</v>
+        <v>0.2384004182683636</v>
       </c>
       <c r="C100">
-        <v>-195.267453687976</v>
+        <v>-198.3425672089265</v>
       </c>
       <c r="D100">
-        <v>49.68654631202402</v>
+        <v>49.23443279107357</v>
       </c>
       <c r="E100">
-        <v>125.154</v>
+        <v>127.777</v>
       </c>
       <c r="F100">
-        <v>257.054</v>
+        <v>259.677</v>
       </c>
       <c r="G100">
         <v>12.1</v>
@@ -9606,37 +9606,37 @@
         <v>22.75333333333334</v>
       </c>
       <c r="M100">
-        <v>60.61333320000001</v>
+        <v>61.23183660000001</v>
       </c>
       <c r="N100">
-        <v>-37.85999986666667</v>
+        <v>-38.47850326666667</v>
       </c>
       <c r="O100">
-        <v>-9.464999966666667</v>
+        <v>-9.619625816666668</v>
       </c>
       <c r="P100">
-        <v>-28.3949999</v>
+        <v>-28.85887745</v>
       </c>
       <c r="Q100">
-        <v>-27.3149999</v>
+        <v>-27.77887745</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.355139124118394</v>
+        <v>2.664478248236788</v>
       </c>
       <c r="T100">
-        <v>26.24394819871658</v>
+        <v>52.48789639743317</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09384623865782279</v>
+        <v>0.09289829685319832</v>
       </c>
       <c r="W100">
-        <v>0.2136710569244854</v>
+        <v>0.2138945816020159</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9644,91 +9644,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3753849546312912</v>
+        <v>0.3715931874127932</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2384004182683636</v>
-      </c>
-      <c r="C101">
-        <v>-198.3425672089265</v>
-      </c>
-      <c r="D101">
-        <v>49.23443279107357</v>
-      </c>
-      <c r="E101">
-        <v>127.777</v>
-      </c>
-      <c r="F101">
-        <v>259.677</v>
-      </c>
-      <c r="G101">
-        <v>12.1</v>
-      </c>
-      <c r="H101">
-        <v>130.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>23.83333333333334</v>
-      </c>
-      <c r="K101">
-        <v>1.08</v>
-      </c>
-      <c r="L101">
-        <v>22.75333333333334</v>
-      </c>
-      <c r="M101">
-        <v>61.23183660000001</v>
-      </c>
-      <c r="N101">
-        <v>-38.47850326666667</v>
-      </c>
-      <c r="O101">
-        <v>-9.619625816666668</v>
-      </c>
-      <c r="P101">
-        <v>-28.85887745</v>
-      </c>
-      <c r="Q101">
-        <v>-27.77887745</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.664478248236788</v>
-      </c>
-      <c r="T101">
-        <v>52.48789639743317</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09289829685319832</v>
-      </c>
-      <c r="W101">
-        <v>0.2138945816020159</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3715931874127932</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
